--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>31.4%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.1%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.4%</t>
+          <t>-554.1%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.7%</t>
+          <t>-151.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.8%</t>
+          <t>-118.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-153.0%</t>
+          <t>-153.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.025279242125166</v>
+        <v>-7.15138198889114</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.34828310299805</v>
+        <v>0.2978420042916605</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-1.003265731997947</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.556791784963096</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.875612851117651</v>
+        <v>-7.001715597883625</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4052574490880967</v>
+        <v>0.3548163503817072</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.9103622407554106</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.609641669395659</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.743337377486765</v>
+        <v>-6.869440124252739</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4535351252874782</v>
+        <v>0.4030940265810887</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.778086767124524</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.684374440321218</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.587599044927023</v>
+        <v>-6.713701791692997</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.518645518999012</v>
+        <v>0.4682044202926221</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6223484345647824</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.780632500544699</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338599246243442</v>
+        <v>-6.464701993009416</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6311517796961028</v>
+        <v>0.5807106809897133</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6223484345647824</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.793538841768358</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.444189236016546</v>
+        <v>-6.57029198278252</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4609398541876426</v>
+        <v>0.4104987554812531</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.7279384243378867</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.602208918305277</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.462924138135143</v>
+        <v>-6.589026884901117</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5019902352172902</v>
+        <v>0.4515491365109003</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.733534433998018</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.647395654386284</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.314984096727544</v>
+        <v>-6.441086843493518</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4412873290921624</v>
+        <v>0.3908462303857725</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.7132135180894604</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.539709281243251</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.262014574473556</v>
+        <v>-6.388117321239529</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4537611517402795</v>
+        <v>0.4033200530338901</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.562777008342167</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.218466167702865</v>
+        <v>-6.344568914468839</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4642199023534626</v>
+        <v>0.4137788036470731</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.555816396247073</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.185102961224096</v>
+        <v>-6.31120570799007</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4920275393261129</v>
+        <v>0.4415864406197234</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.570278750628217</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.076843824101575</v>
+        <v>-6.202946570867549</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5298633146343166</v>
+        <v>0.4794222159279271</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.564810871087412</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.953552689284444</v>
+        <v>-6.079655436050418</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5766778625717461</v>
+        <v>0.5262367638653562</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.5369528610183411</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.636283645988267</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.932403490381001</v>
+        <v>-6.058506237146974</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5928385203704485</v>
+        <v>0.542397421664059</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.5158036621148977</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.656674143567658</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.688638048397556</v>
+        <v>-5.81474079516353</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.686125405510877</v>
+        <v>0.6356843068044875</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.5158036621148977</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.652454851914709</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.586875228120261</v>
+        <v>-5.712977974886235</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7289548475418108</v>
+        <v>0.6785137488354214</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.502584593722469</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.662510606870182</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.337024834171187</v>
+        <v>-5.463127580937161</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8216370801051429</v>
+        <v>0.7711959813987534</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.502584593722469</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.655252681853884</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.161132741703755</v>
+        <v>-5.287235488469728</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955930406127646</v>
+        <v>0.8451519419063751</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.502584593722469</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.658851805374533</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.989686278681291</v>
+        <v>-5.115789025447264</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9774991318763036</v>
+        <v>0.9270580331699145</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.3311381307000059</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.775047189242564</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.915396712942952</v>
+        <v>-5.041499459708925</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006235435787936</v>
+        <v>0.9557943370815472</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.2568485649616666</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.818641406301865</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.851760970709018</v>
+        <v>-4.977863717474991</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036384533735827</v>
+        <v>0.985943435029438</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.193212822727732</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.861517652696543</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.740334211383098</v>
+        <v>-4.866436958149071</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.062149496249991</v>
+        <v>1.011708397543602</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.193212822727732</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.842711911480338</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.499903714578237</v>
+        <v>-4.62600646134421</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.160064771596812</v>
+        <v>1.109623672890423</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.04721767407712824</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>2.988713286188132</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.427661146407043</v>
+        <v>-4.553763893173016</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.192891112700111</v>
+        <v>1.142450013993721</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.04721767407712824</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>2.992642600022952</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.409947459529177</v>
+        <v>-4.53605020629515</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.200655171368597</v>
+        <v>1.150214072662207</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.05039900297404504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.070891629338026</v>
+        <v>2.995229981278442</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.30114257404945</v>
+        <v>-4.427245320815423</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.241175196780481</v>
+        <v>1.190734098074092</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.05039900297404504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.06788970055802</v>
+        <v>2.992228052498436</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08112177601244</v>
+        <v>-4.207224522778413</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.330762553005899</v>
+        <v>1.28032145429951</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.1916188480420253</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.154200644609422</v>
+        <v>3.078538996549838</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948254086949162</v>
+        <v>-4.074356833715135</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399803811433034</v>
+        <v>1.349362712726645</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.1916188480420253</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.170094827411245</v>
+        <v>3.094433179351661</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828081003584662</v>
+        <v>-3.954183750350636</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449018889219135</v>
+        <v>1.398577790512746</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.437894678172498</v>
+        <v>0.3117919314065242</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.243344521870247</v>
+        <v>3.167682873810663</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.683408858484925</v>
+        <v>-3.809511605250899</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.51697584982047</v>
+        <v>1.466534751114081</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5825668232722354</v>
+        <v>0.4564640765062616</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.340235911491529</v>
+        <v>3.264574263431945</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.743283685842617</v>
+        <v>-3.869386432608591</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479063410278819</v>
+        <v>1.428622311572429</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.3965892491485695</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.29034850647834</v>
+        <v>3.214686858418755</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.62346345493178</v>
+        <v>-3.749566201697754</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.542280671877363</v>
+        <v>1.491839573170973</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.3965892491485695</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.305637675712548</v>
+        <v>3.229976027652964</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.625933161393586</v>
+        <v>-3.75203590815956</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.448936988615082</v>
+        <v>1.398495889908692</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5202222894527371</v>
+        <v>0.3941195426867634</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.211800051157906</v>
+        <v>3.136138403098322</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.694303347717596</v>
+        <v>-3.82040609448357</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.340850775570779</v>
+        <v>1.29040967686439</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.136627332064936</v>
+        <v>3.060965684005352</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.708091400564642</v>
+        <v>-3.834194147330616</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325772263063852</v>
+        <v>1.275331164357462</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.127064040696828</v>
+        <v>3.051402392637244</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.763611476457232</v>
+        <v>-3.889714223223206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.440595069399018</v>
+        <v>1.390153970692629</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.26409487738903</v>
+        <v>3.188433229329446</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.588137216664763</v>
+        <v>-3.714239963430737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.515352005307794</v>
+        <v>1.464910906601404</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.268662109380818</v>
+        <v>3.193000461321234</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.699073469306011</v>
+        <v>-3.825176216071985</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.446719533012502</v>
+        <v>1.396278434306112</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.244404138142025</v>
+        <v>3.168742490082441</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.665409923833729</v>
+        <v>-3.791512670599703</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.388723264602864</v>
+        <v>1.338282165896475</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4370587871952601</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.193140578826844</v>
+        <v>3.117478930767259</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.605557304630006</v>
+        <v>-3.73166005139598</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.422836698716486</v>
+        <v>1.372395600010096</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4370587871952601</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.203312965258976</v>
+        <v>3.127651317199392</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.519313841603629</v>
+        <v>-3.645416588369603</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.452280354500897</v>
+        <v>1.401839255794507</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4370587871952601</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.198259235832837</v>
+        <v>3.122597587773252</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.564620661002609</v>
+        <v>-3.690723407768583</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.425933402185831</v>
+        <v>1.375492303479441</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.3962486241860294</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.165548913471823</v>
+        <v>3.089887265412239</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.59365376570491</v>
+        <v>-3.719756512470884</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.414872033338011</v>
+        <v>1.364430934631622</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.3962486241860294</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.166100786504925</v>
+        <v>3.090439138445341</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.500843284254051</v>
+        <v>-3.626946031020025</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.381268917809721</v>
+        <v>1.330827819103331</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6151618524028625</v>
+        <v>0.4890591056368887</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.151059767266806</v>
+        <v>3.075398119207222</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.545232753583479</v>
+        <v>-3.671335500349453</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.365386606002551</v>
+        <v>1.314945507296161</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5707723830734348</v>
+        <v>0.444669636307461</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.126299561593751</v>
+        <v>3.050637913534166</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.432561535347229</v>
+        <v>-3.558664282113202</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.405530801808774</v>
+        <v>1.355089703102384</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.683443601309685</v>
+        <v>0.5573408545437112</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.188978001047224</v>
+        <v>3.113316352987639</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.320184534164556</v>
+        <v>-3.44628728093053</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.45597289811251</v>
+        <v>1.40553179940612</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.683443601309685</v>
+        <v>0.5573408545437112</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.194469296877891</v>
+        <v>3.118807648818307</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.347964932065909</v>
+        <v>-3.474067678831883</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.456357940720508</v>
+        <v>1.405916842014118</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6556632034083318</v>
+        <v>0.5295604566423581</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.189298259905618</v>
+        <v>3.113636611846034</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.466345604796047</v>
+        <v>-3.592448351562021</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.247361391629106</v>
+        <v>1.196920292922716</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4623426044913819</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.987323268615686</v>
+        <v>2.911661620556101</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.574959683239379</v>
+        <v>-3.701062430005353</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.324065420970979</v>
+        <v>1.273624322264589</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4623426044913819</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.107472929334891</v>
+        <v>3.031811281275307</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.539550644991236</v>
+        <v>-3.66565339175721</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.352742062372559</v>
+        <v>1.302300963666169</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4623426044913819</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.121985955437214</v>
+        <v>3.04632430737763</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.501166982433085</v>
+        <v>-3.627269729199059</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.365514968738188</v>
+        <v>1.315073870031799</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.500726267049533</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.142435594314474</v>
+        <v>3.06677394625489</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.324050652397919</v>
+        <v>-3.450153399163892</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.433090529597556</v>
+        <v>1.382649430891167</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.500726267049533</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.139164623159775</v>
+        <v>3.063502975100191</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.369142897231464</v>
+        <v>-3.495245643997438</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.415737023426051</v>
+        <v>1.365295924719662</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.564932970646117</v>
+        <v>0.4388302238801433</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.102710389020055</v>
+        <v>3.02704874096047</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.189767475992697</v>
+        <v>-3.31587022275867</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.481274167227973</v>
+        <v>1.430833068521583</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7217097288168357</v>
+        <v>0.5956069820508619</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.190563419228901</v>
+        <v>3.114901771169316</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.234781689513303</v>
+        <v>-3.360884436279277</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.44407593715132</v>
+        <v>1.39363483844493</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6913608335022311</v>
+        <v>0.5652580867362573</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.153161537371727</v>
+        <v>3.077499889312143</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.501786199785738</v>
+        <v>-3.627888946551712</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.342965695381292</v>
+        <v>1.292524596674902</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4969977954592826</v>
+        <v>0.3708950486933087</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.042235276884904</v>
+        <v>2.96657362882532</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.602983981222911</v>
+        <v>-3.729086727988885</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.301690504702924</v>
+        <v>1.251249405996534</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.3024862351479896</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.000393910654214</v>
+        <v>2.92473226259463</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.596473014608598</v>
+        <v>-3.722575761374572</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.301894852902966</v>
+        <v>1.251453754196576</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.3024862351479896</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.99799387220853</v>
+        <v>2.922332224148946</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.577434886901301</v>
+        <v>-3.703537633667275</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.306034823194129</v>
+        <v>1.25559372448774</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.244302623816795</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.959608424618059</v>
+        <v>2.883946776558474</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.608561518051919</v>
+        <v>-3.734664264817893</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.471166039672563</v>
+        <v>1.420724940966173</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.244302623816795</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.137190293556739</v>
+        <v>3.061528645497155</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.622428279385836</v>
+        <v>-3.74853102615181</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.466452664125129</v>
+        <v>1.41601156541874</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.2064447070829721</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.115308872502579</v>
+        <v>3.039647224442995</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.577624107845907</v>
+        <v>-3.70372685461188</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.490382863138027</v>
+        <v>1.439941764431638</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.2064447070829721</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.121317402899505</v>
+        <v>3.045655754839921</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.429881137610904</v>
+        <v>-3.555983884376878</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.447430272509228</v>
+        <v>1.396989173802838</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.3742520643178552</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.119952038517634</v>
+        <v>3.04429039045805</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.531895820142125</v>
+        <v>-3.657998566908099</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.40941802102822</v>
+        <v>1.358976922321831</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.3742520643178552</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.122745660049115</v>
+        <v>3.047084011989531</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.525743114089341</v>
+        <v>-3.651845860855315</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.412541451840992</v>
+        <v>1.362100353134603</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5065075171366133</v>
+        <v>0.3804047703706395</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.127099632072444</v>
+        <v>3.05143798401286</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.542552412239842</v>
+        <v>-3.668655159005816</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.404898209320902</v>
+        <v>1.354457110614512</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.3635954722201379</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.116094529922254</v>
+        <v>3.040432881862669</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.480254413463721</v>
+        <v>-3.606357160229694</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.496152962628172</v>
+        <v>1.445711863921782</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.3635954722201379</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182430083719074</v>
+        <v>3.10676843565949</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.278464215798563</v>
+        <v>-3.404566962564537</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.379161043408362</v>
+        <v>1.328719944701972</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.687716411155266</v>
+        <v>0.5616136643892923</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.103533000734694</v>
+        <v>3.02787135267511</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.329350928484757</v>
+        <v>-3.455453675250731</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.429096590656059</v>
+        <v>1.37865549194967</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6368296984690716</v>
+        <v>0.5107269517030978</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143291205445153</v>
+        <v>3.067629557385569</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.427091473109732</v>
+        <v>-3.553194219875706</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.404628108922113</v>
+        <v>1.354187010215724</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6209404203360913</v>
+        <v>0.4948376735701175</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.148385374681408</v>
+        <v>3.072723726621824</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.487300771115016</v>
+        <v>-3.61340351788099</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.379080370544671</v>
+        <v>1.328639271838282</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5607311223308068</v>
+        <v>0.434628375564833</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.110795776702909</v>
+        <v>3.035134128643325</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.410878724683089</v>
+        <v>-3.536981471449063</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.40814080715737</v>
+        <v>1.357699708450981</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5607311223308068</v>
+        <v>0.434628375564833</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.109287394742838</v>
+        <v>3.033625746683254</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.366505593044521</v>
+        <v>-3.492608339810495</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.425752927248234</v>
+        <v>1.375311828541844</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6051042539693754</v>
+        <v>0.4790015072034016</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.135774141161415</v>
+        <v>3.060112493101831</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.243671372157353</v>
+        <v>-3.369774118923327</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.469280409741691</v>
+        <v>1.418839311035302</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6051042539693754</v>
+        <v>0.4790015072034016</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.130167935300006</v>
+        <v>3.054506287240421</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.196015641596298</v>
+        <v>-3.322118388362272</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.494724458993918</v>
+        <v>1.444283360287529</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.652759984530431</v>
+        <v>0.5266572377644573</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.165143130664444</v>
+        <v>3.089481482604859</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.095497483097543</v>
+        <v>-3.221600229863517</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.539824095768145</v>
+        <v>1.489382997061755</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7532781430291856</v>
+        <v>0.6271753962632118</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.230346399138421</v>
+        <v>3.154684751078837</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.156164073499932</v>
+        <v>-3.282266820265906</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.502312132083061</v>
+        <v>1.451871033376672</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6715798263106519</v>
+        <v>0.5454770795446782</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.168082081583173</v>
+        <v>3.092420433523589</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.111325671891534</v>
+        <v>-3.237428418657508</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.524345195337049</v>
+        <v>1.47390409663066</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6761232592555214</v>
+        <v>0.5500205124895476</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.174905843960723</v>
+        <v>3.099244195901139</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.130824128133542</v>
+        <v>-3.256926874899516</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.520706752471324</v>
+        <v>1.470265653764935</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6280386179756171</v>
+        <v>0.5019358712096433</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.150215998823859</v>
+        <v>3.074554350764275</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.086621291047642</v>
+        <v>-3.212724037813616</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.544267489833521</v>
+        <v>1.493826391127132</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6722414550615176</v>
+        <v>0.5461387082955438</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.182617303603236</v>
+        <v>3.106955655543652</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.123600318711085</v>
+        <v>-3.249703065477059</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.527885879237392</v>
+        <v>1.477444780531002</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7092153568528481</v>
+        <v>0.5831126100868743</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.203211645147282</v>
+        <v>3.127549997087698</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.965308901171813</v>
+        <v>-3.091411647937787</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.64245021143614</v>
+        <v>1.592009112729751</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7092153568528481</v>
+        <v>0.5831126100868743</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.254459410330322</v>
+        <v>3.178797762270738</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.757666897537337</v>
+        <v>-2.883769644303311</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.723947717484184</v>
+        <v>1.673506618777794</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9168573604873242</v>
+        <v>0.7907546137213505</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.37748531710526</v>
+        <v>3.301823669045676</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.706634804814809</v>
+        <v>-2.832737551580783</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.739308782811465</v>
+        <v>1.688867684105076</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9678894532098522</v>
+        <v>0.8417867064438784</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.403052800977047</v>
+        <v>3.327391152917463</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.641410623687603</v>
+        <v>-2.767513370453577</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.782585859355052</v>
+        <v>1.732144760648663</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.033113634337058</v>
+        <v>0.9070108875710841</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.459374713746076</v>
+        <v>3.383713065686492</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.60398360361647</v>
+        <v>-2.730086350382444</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.793517639682786</v>
+        <v>1.743076540976396</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.038365172366239</v>
+        <v>0.9122624256002657</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.458486608862865</v>
+        <v>3.382824960803281</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.624095259651178</v>
+        <v>-2.750198006417152</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.786729769600143</v>
+        <v>1.736288670893753</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.049392517363658</v>
+        <v>0.9232897705976849</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.466359808192557</v>
+        <v>3.390698160132973</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.570350445223973</v>
+        <v>-2.696453191989947</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.968785466392236</v>
+        <v>1.918344367685846</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.059455826804121</v>
+        <v>0.9333530800381469</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.632955564878045</v>
+        <v>3.557293916818461</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.495568184198961</v>
+        <v>-2.621670930964934</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.118811280020058</v>
+        <v>2.068370181313668</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.134238087829133</v>
+        <v>1.00813534106316</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.79793783071087</v>
+        <v>3.722276182651286</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.469484099935153</v>
+        <v>-2.595586846701126</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.12095288973944</v>
+        <v>2.07051179103305</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.134238087829133</v>
+        <v>1.00813534106316</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.789645806724729</v>
+        <v>3.713984158665145</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.391352919086206</v>
+        <v>-2.51745566585218</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.150398557662798</v>
+        <v>2.099957458956409</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.208414898712818</v>
+        <v>1.082312151946844</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.832345088838719</v>
+        <v>3.756683440779135</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.382460457692923</v>
+        <v>-2.508563204458897</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.171509947946903</v>
+        <v>2.121068849240513</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.208414898712818</v>
+        <v>1.082312151946844</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.84989949456551</v>
+        <v>3.774237846505926</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.550936574662801</v>
+        <v>-2.677039321428774</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.095974548563536</v>
+        <v>2.045533449857146</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.180467062996237</v>
+        <v>1.054364316230264</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.824985840540146</v>
+        <v>3.749324192480562</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.853137045801217</v>
+        <v>-1.979239792567191</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.356364057296031</v>
+        <v>2.305922958589641</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.110119003625826</v>
+        <v>0.9840162568598529</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.764046702105761</v>
+        <v>3.688385054046177</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.830415942118065</v>
+        <v>-1.956518688884039</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.356116521266197</v>
+        <v>2.305675422559807</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.110119003625826</v>
+        <v>0.9840162568598529</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.754710724602666</v>
+        <v>3.679049076543082</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.959617755412107</v>
+        <v>-2.085720502178081</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.463341921799748</v>
+        <v>2.412900823093359</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9809171903317842</v>
+        <v>0.8548144435658107</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.836095762477409</v>
+        <v>3.760434114417825</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.114398762190362</v>
+        <v>-2.240501508956337</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.438507341582093</v>
+        <v>2.388066242875703</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.947549516277308</v>
+        <v>0.8214467695113346</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.85315298053837</v>
+        <v>3.777491332478786</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.107344071975189</v>
+        <v>-2.233446818741163</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.438004573657707</v>
+        <v>2.387563474951318</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9546042064924818</v>
+        <v>0.8285014597265083</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.854061150657019</v>
+        <v>3.778399502597436</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.080392847648701</v>
+        <v>-2.206495594414675</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.458791217033044</v>
+        <v>2.408350118326655</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8433818057542275</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.872995511918393</v>
+        <v>3.797333863858809</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.216345855705017</v>
+        <v>-2.342448602470991</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.588513145955478</v>
+        <v>2.538072047249088</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8433818057542275</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.057098644063353</v>
+        <v>3.981436996003769</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.238753973509889</v>
+        <v>-2.364856720275863</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.571666593736522</v>
+        <v>2.521225495030132</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8433818057542275</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.049215338966346</v>
+        <v>3.973553690906762</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.386759740989288</v>
+        <v>-2.512862487755263</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.5145182862944</v>
+        <v>2.46407718758801</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8827575436566595</v>
+        <v>0.756654796890686</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999233133197858</v>
+        <v>3.923571485138274</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.396200666877818</v>
+        <v>-2.522303413643793</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.566995633660835</v>
+        <v>2.516554534954445</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.005184661200051</v>
+        <v>0.8790819144340775</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.12894312144574</v>
+        <v>4.053281473386156</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.44847427421346</v>
+        <v>-2.574577020979434</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.548977285271879</v>
+        <v>2.498536186565489</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8268083070984362</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100470051589657</v>
+        <v>4.024808403530072</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.524804251814365</v>
+        <v>-2.65090699858034</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.516557107125292</v>
+        <v>2.466116008418902</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8268083070984362</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098581864483432</v>
+        <v>4.022920216423847</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.636561204429666</v>
+        <v>-2.762663951195641</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.466674555682034</v>
+        <v>2.416233456975644</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8411541012491086</v>
+        <v>0.7150513544831352</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.026347922517113</v>
+        <v>3.950686274457529</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.634720185371415</v>
+        <v>-2.76082293213739</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.465844973515487</v>
+        <v>2.415403874809097</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7163195811546036</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.025542868730146</v>
+        <v>3.949881220670562</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.767021477468969</v>
+        <v>-2.893124224234943</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.425997863542384</v>
+        <v>2.375556764835994</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7163195811546036</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.038616275596065</v>
+        <v>3.962954627536481</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.768583120283829</v>
+        <v>-2.894685867049803</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.42537320641644</v>
+        <v>2.37493210771005</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7163195811546036</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.038616275596065</v>
+        <v>3.962954627536481</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.796483907393302</v>
+        <v>-2.922586654159276</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.412736932699652</v>
+        <v>2.362295833993262</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8078254037776422</v>
+        <v>0.6817226570116688</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.016382162237306</v>
+        <v>3.940720514177722</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.919010010096196</v>
+        <v>-3.04511275686217</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.360490935595694</v>
+        <v>2.310049836889304</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6852993010747483</v>
+        <v>0.5591965543087749</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.939630944592769</v>
+        <v>3.863969296533185</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.939071331372702</v>
+        <v>-3.065174078138677</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.419172366675595</v>
+        <v>2.368731267969205</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6652379797982413</v>
+        <v>0.5391352330322678</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.994300111417368</v>
+        <v>3.918638463357784</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199806</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.195792149367526</v>
+        <v>-3.321894896133501</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.456795758479513</v>
+        <v>2.406354659773123</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.069563085932926</v>
+        <v>3.993901437873342</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.349778567143667</v>
+        <v>-3.475881313909642</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.464181460514696</v>
+        <v>2.413740361808306</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.138543355078566</v>
+        <v>4.062881707018982</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.299256663316001</v>
+        <v>-3.425359410081976</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.470441424165883</v>
+        <v>2.420000325459493</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.124594557198687</v>
+        <v>4.048932909139102</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.551731817323725</v>
+        <v>-3.6778345640897</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.381321851618207</v>
+        <v>2.330880752911817</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.136465046254101</v>
+        <v>4.060803398194517</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.821204619245433</v>
+        <v>-3.947307366011408</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.274743265368468</v>
+        <v>2.224302166662078</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.137675580773045</v>
+        <v>4.062013932713461</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.978748690974875</v>
+        <v>-4.10485143774085</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.215847378904013</v>
+        <v>2.165406280197623</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.489921600514152</v>
+        <v>0.3638188537481785</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.101656239916202</v>
+        <v>4.025994591856617</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301344</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.256713086558149</v>
+        <v>-4.382815833324123</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.099739473406893</v>
+        <v>2.049298374700503</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2741991194626943</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.0429622520811</v>
+        <v>3.967300604021516</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.66797646721547</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.37368077919704</v>
+        <v>-4.499783525963014</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.215156453050381</v>
+        <v>2.164715354343991</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2741991194626943</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.205166308780145</v>
+        <v>4.12950466072056</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.458398721417993</v>
+        <v>-4.584501468183968</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.176115914125814</v>
+        <v>2.125674815419424</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3151858373006214</v>
+        <v>0.1890830905346479</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.148943329387131</v>
+        <v>4.073281681327547</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253286</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.540333539686876</v>
+        <v>-4.666436286452851</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.153571404386752</v>
+        <v>2.103130305680362</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3052510917135412</v>
+        <v>0.1791483449475677</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.153211899603374</v>
+        <v>4.07755025154379</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.486595366286614</v>
+        <v>-4.612698113052589</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.183992312202759</v>
+        <v>2.133551213496369</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3589892651138033</v>
+        <v>0.2328865183478298</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.194380442099433</v>
+        <v>4.118718794039849</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616949</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.376589082809392</v>
+        <v>-4.502691829575367</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.220147712837823</v>
+        <v>2.169706614131433</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3821938370310785</v>
+        <v>0.256091090265105</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.200456072493974</v>
+        <v>4.12479442443439</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203662</v>
+        <v>3.785578085203664</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.233529507068466</v>
+        <v>-4.359632253834441</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.281621553856167</v>
+        <v>2.231180455149778</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3902072636210578</v>
+        <v>0.2641045168550843</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.209514139169936</v>
+        <v>4.133852491110352</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436928</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.932082781596629</v>
+        <v>-4.058185528362603</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.409461126927439</v>
+        <v>2.359020028221049</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5655512423269216</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.397643057335575</v>
+        <v>4.321981409275991</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.987037978039698</v>
+        <v>-4.113140724805673</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.388450226102921</v>
+        <v>2.338009127396532</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5655512423269216</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.398614235088285</v>
+        <v>4.322952587028701</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.935999602033178</v>
+        <v>-4.062102348799153</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.409708480885285</v>
+        <v>2.359267382178895</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5655512423269216</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.399457139468041</v>
+        <v>4.323795491408457</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354683</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.894860307166547</v>
+        <v>-4.020963053932522</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.445202297706083</v>
+        <v>2.394761198999693</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7327932839595258</v>
+        <v>0.6066905371935524</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.443178815262165</v>
+        <v>4.367517167202581</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.82576709308562</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.784254167086945</v>
+        <v>-3.91035691385292</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.305628749861858</v>
+        <v>2.255187651155468</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8433994240391278</v>
+        <v>0.7172966772731544</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.325726495433861</v>
+        <v>4.250064847374277</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.908738632633159</v>
+        <v>3.594656226348546</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.917897644716175</v>
+        <v>-3.925512563074596</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.25567340288413</v>
+        <v>2.252627435540761</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7097559464098978</v>
+        <v>0.7021410280514778</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.249042452930286</v>
+        <v>4.244473501915234</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>456.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-554.1%</t>
+          <t>-553.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.0%</t>
+          <t>-140.5%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-118.0%</t>
+          <t>-127.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-153.8%</t>
+          <t>-152.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-10.9%</t>
         </is>
       </c>
     </row>
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.15138198889114</v>
+        <v>-7.025279242125166</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2978420042916605</v>
+        <v>0.34828310299805</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.003265731997947</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.556791784963096</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.001715597883625</v>
+        <v>-6.875612851117651</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3548163503817072</v>
+        <v>0.4052574490880967</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9103622407554106</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.609641669395659</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.869440124252739</v>
+        <v>-6.743337377486765</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4030940265810887</v>
+        <v>0.4535351252874782</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.778086767124524</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.684374440321218</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.713701791692997</v>
+        <v>-6.587599044927023</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4682044202926221</v>
+        <v>0.518645518999012</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6223484345647824</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.780632500544699</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.464701993009416</v>
+        <v>-6.338599246243442</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5807106809897133</v>
+        <v>0.6311517796961028</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6223484345647824</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.793538841768358</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.57029198278252</v>
+        <v>-6.444189236016546</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4104987554812531</v>
+        <v>0.4609398541876426</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7279384243378867</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.602208918305277</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.589026884901117</v>
+        <v>-6.462924138135143</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4515491365109003</v>
+        <v>0.5019902352172902</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.733534433998018</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.647395654386284</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.441086843493518</v>
+        <v>-6.314984096727544</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3908462303857725</v>
+        <v>0.4412873290921624</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7132135180894604</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.539709281243251</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.388117321239529</v>
+        <v>-6.262014574473556</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4033200530338901</v>
+        <v>0.4537611517402795</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.562777008342167</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.344568914468839</v>
+        <v>-6.218466167702865</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4137788036470731</v>
+        <v>0.4642199023534626</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.555816396247073</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.31120570799007</v>
+        <v>-6.185102961224096</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4415864406197234</v>
+        <v>0.4920275393261129</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.570278750628217</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.202946570867549</v>
+        <v>-6.076843824101575</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4794222159279271</v>
+        <v>0.5298633146343166</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.564810871087412</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.079655436050418</v>
+        <v>-5.953552689284444</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5262367638653562</v>
+        <v>0.5766778625717461</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5369528610183411</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.636283645988267</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.058506237146974</v>
+        <v>-5.932403490381001</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.542397421664059</v>
+        <v>0.5928385203704485</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5158036621148977</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.656674143567658</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.81474079516353</v>
+        <v>-5.688638048397556</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6356843068044875</v>
+        <v>0.686125405510877</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5158036621148977</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.652454851914709</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.712977974886235</v>
+        <v>-5.586875228120261</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6785137488354214</v>
+        <v>0.7289548475418108</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.502584593722469</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.662510606870182</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.463127580937161</v>
+        <v>-5.337024834171187</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7711959813987534</v>
+        <v>0.8216370801051429</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.502584593722469</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.655252681853884</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.287235488469728</v>
+        <v>-5.161132741703755</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8451519419063751</v>
+        <v>0.8955930406127646</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.502584593722469</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.658851805374533</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.115789025447264</v>
+        <v>-4.989686278681291</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9270580331699145</v>
+        <v>0.9774991318763036</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3311381307000059</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.775047189242564</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.041499459708925</v>
+        <v>-4.915396712942952</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9557943370815472</v>
+        <v>1.006235435787936</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2568485649616666</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.818641406301865</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.977863717474991</v>
+        <v>-4.851760970709018</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.985943435029438</v>
+        <v>1.036384533735827</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.193212822727732</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.861517652696543</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.866436958149071</v>
+        <v>-4.740334211383098</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.011708397543602</v>
+        <v>1.062149496249991</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.193212822727732</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.842711911480338</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.62600646134421</v>
+        <v>-4.499903714578237</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.109623672890423</v>
+        <v>1.160064771596812</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.04721767407712824</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.988713286188132</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.553763893173016</v>
+        <v>-4.427661146407043</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.142450013993721</v>
+        <v>1.192891112700111</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.04721767407712824</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.992642600022952</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.53605020629515</v>
+        <v>-4.409947459529177</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.150214072662207</v>
+        <v>1.200655171368597</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.05039900297404504</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.995229981278442</v>
+        <v>3.070891629338026</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.427245320815423</v>
+        <v>-4.30114257404945</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.190734098074092</v>
+        <v>1.241175196780481</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.05039900297404504</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.992228052498436</v>
+        <v>3.06788970055802</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.207224522778413</v>
+        <v>-4.08112177601244</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.28032145429951</v>
+        <v>1.330762553005899</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1916188480420253</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.078538996549838</v>
+        <v>3.154200644609422</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.074356833715135</v>
+        <v>-3.948254086949162</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.349362712726645</v>
+        <v>1.399803811433034</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1916188480420253</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.094433179351661</v>
+        <v>3.170094827411245</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.954183750350636</v>
+        <v>-3.828081003584662</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.398577790512746</v>
+        <v>1.449018889219135</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3117919314065242</v>
+        <v>0.437894678172498</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.167682873810663</v>
+        <v>3.243344521870247</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.809511605250899</v>
+        <v>-3.683408858484925</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.466534751114081</v>
+        <v>1.51697584982047</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4564640765062616</v>
+        <v>0.5825668232722354</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.264574263431945</v>
+        <v>3.340235911491529</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.869386432608591</v>
+        <v>-3.743283685842617</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.428622311572429</v>
+        <v>1.479063410278819</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3965892491485695</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.214686858418755</v>
+        <v>3.29034850647834</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.749566201697754</v>
+        <v>-3.62346345493178</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.491839573170973</v>
+        <v>1.542280671877363</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3965892491485695</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.229976027652964</v>
+        <v>3.305637675712548</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.75203590815956</v>
+        <v>-3.625933161393586</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.398495889908692</v>
+        <v>1.448936988615082</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3941195426867634</v>
+        <v>0.5202222894527371</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.136138403098322</v>
+        <v>3.211800051157906</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.82040609448357</v>
+        <v>-3.694303347717596</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.29040967686439</v>
+        <v>1.340850775570779</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.060965684005352</v>
+        <v>3.136627332064936</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.834194147330616</v>
+        <v>-3.708091400564642</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.275331164357462</v>
+        <v>1.325772263063852</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.051402392637244</v>
+        <v>3.127064040696828</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.889714223223206</v>
+        <v>-3.763611476457232</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.390153970692629</v>
+        <v>1.440595069399018</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.188433229329446</v>
+        <v>3.26409487738903</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.714239963430737</v>
+        <v>-3.588137216664763</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.464910906601404</v>
+        <v>1.515352005307794</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.193000461321234</v>
+        <v>3.268662109380818</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.825176216071985</v>
+        <v>-3.699073469306011</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.396278434306112</v>
+        <v>1.446719533012502</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.168742490082441</v>
+        <v>3.244404138142025</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.791512670599703</v>
+        <v>-3.665409923833729</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.338282165896475</v>
+        <v>1.388723264602864</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4370587871952601</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.117478930767259</v>
+        <v>3.193140578826844</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.73166005139598</v>
+        <v>-3.605557304630006</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.372395600010096</v>
+        <v>1.422836698716486</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4370587871952601</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.127651317199392</v>
+        <v>3.203312965258976</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.645416588369603</v>
+        <v>-3.519313841603629</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.401839255794507</v>
+        <v>1.452280354500897</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4370587871952601</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.122597587773252</v>
+        <v>3.198259235832837</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.690723407768583</v>
+        <v>-3.564620661002609</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.375492303479441</v>
+        <v>1.425933402185831</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3962486241860294</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.089887265412239</v>
+        <v>3.165548913471823</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.719756512470884</v>
+        <v>-3.59365376570491</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.364430934631622</v>
+        <v>1.414872033338011</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3962486241860294</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.090439138445341</v>
+        <v>3.166100786504925</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.626946031020025</v>
+        <v>-3.500843284254051</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.330827819103331</v>
+        <v>1.381268917809721</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4890591056368887</v>
+        <v>0.6151618524028625</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.075398119207222</v>
+        <v>3.151059767266806</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.671335500349453</v>
+        <v>-3.545232753583479</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.314945507296161</v>
+        <v>1.365386606002551</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.444669636307461</v>
+        <v>0.5707723830734348</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.050637913534166</v>
+        <v>3.126299561593751</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.558664282113202</v>
+        <v>-3.432561535347229</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.355089703102384</v>
+        <v>1.405530801808774</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5573408545437112</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.113316352987639</v>
+        <v>3.188978001047224</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.44628728093053</v>
+        <v>-3.320184534164556</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.40553179940612</v>
+        <v>1.45597289811251</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5573408545437112</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.118807648818307</v>
+        <v>3.194469296877891</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.474067678831883</v>
+        <v>-3.347964932065909</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.405916842014118</v>
+        <v>1.456357940720508</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5295604566423581</v>
+        <v>0.6556632034083318</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.113636611846034</v>
+        <v>3.189298259905618</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.592448351562021</v>
+        <v>-3.466345604796047</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.196920292922716</v>
+        <v>1.247361391629106</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4623426044913819</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.911661620556101</v>
+        <v>2.987323268615686</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.701062430005353</v>
+        <v>-3.574959683239379</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.273624322264589</v>
+        <v>1.324065420970979</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4623426044913819</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.031811281275307</v>
+        <v>3.107472929334891</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.66565339175721</v>
+        <v>-3.539550644991236</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.302300963666169</v>
+        <v>1.352742062372559</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4623426044913819</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.04632430737763</v>
+        <v>3.121985955437214</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.627269729199059</v>
+        <v>-3.501166982433085</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.315073870031799</v>
+        <v>1.365514968738188</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.500726267049533</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.06677394625489</v>
+        <v>3.142435594314474</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.450153399163892</v>
+        <v>-3.324050652397919</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.382649430891167</v>
+        <v>1.433090529597556</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.500726267049533</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.063502975100191</v>
+        <v>3.139164623159775</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.495245643997438</v>
+        <v>-3.369142897231464</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.365295924719662</v>
+        <v>1.415737023426051</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4388302238801433</v>
+        <v>0.564932970646117</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.02704874096047</v>
+        <v>3.102710389020055</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.31587022275867</v>
+        <v>-3.189767475992697</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.430833068521583</v>
+        <v>1.481274167227973</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5956069820508619</v>
+        <v>0.7217097288168357</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.114901771169316</v>
+        <v>3.190563419228901</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.360884436279277</v>
+        <v>-3.234781689513303</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.39363483844493</v>
+        <v>1.44407593715132</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5652580867362573</v>
+        <v>0.6913608335022311</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.077499889312143</v>
+        <v>3.153161537371727</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.627888946551712</v>
+        <v>-3.501786199785738</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.292524596674902</v>
+        <v>1.342965695381292</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3708950486933087</v>
+        <v>0.4969977954592826</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.96657362882532</v>
+        <v>3.042235276884904</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.729086727988885</v>
+        <v>-3.602983981222911</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.251249405996534</v>
+        <v>1.301690504702924</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3024862351479896</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.92473226259463</v>
+        <v>3.000393910654214</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.722575761374572</v>
+        <v>-3.596473014608598</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.251453754196576</v>
+        <v>1.301894852902966</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3024862351479896</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.922332224148946</v>
+        <v>2.99799387220853</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.703537633667275</v>
+        <v>-3.577434886901301</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.25559372448774</v>
+        <v>1.306034823194129</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.244302623816795</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.883946776558474</v>
+        <v>2.959608424618059</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.734664264817893</v>
+        <v>-3.608561518051919</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.420724940966173</v>
+        <v>1.471166039672563</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.244302623816795</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.061528645497155</v>
+        <v>3.137190293556739</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.74853102615181</v>
+        <v>-3.622428279385836</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.41601156541874</v>
+        <v>1.466452664125129</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2064447070829721</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.039647224442995</v>
+        <v>3.115308872502579</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.70372685461188</v>
+        <v>-3.577624107845907</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.439941764431638</v>
+        <v>1.490382863138027</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2064447070829721</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.045655754839921</v>
+        <v>3.121317402899505</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.555983884376878</v>
+        <v>-3.429881137610904</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.396989173802838</v>
+        <v>1.447430272509228</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3742520643178552</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.04429039045805</v>
+        <v>3.119952038517634</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.657998566908099</v>
+        <v>-3.531895820142125</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.358976922321831</v>
+        <v>1.40941802102822</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3742520643178552</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.047084011989531</v>
+        <v>3.122745660049115</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.651845860855315</v>
+        <v>-3.525743114089341</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.362100353134603</v>
+        <v>1.412541451840992</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3804047703706395</v>
+        <v>0.5065075171366133</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.05143798401286</v>
+        <v>3.127099632072444</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.822275598530586</v>
+        <v>2.92281506170616</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.668655159005816</v>
+        <v>-3.542552412239842</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.354457110614512</v>
+        <v>1.505437672496476</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3635954722201379</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.040432881862669</v>
+        <v>3.216633993097827</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.888611152327407</v>
+        <v>2.989150615502981</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.606357160229694</v>
+        <v>-3.480254413463721</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.445711863921782</v>
+        <v>1.596692425803746</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3635954722201379</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.10676843565949</v>
+        <v>3.282969546894648</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.690903154041534</v>
+        <v>2.791442617217108</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.404566962564537</v>
+        <v>-3.278464215798563</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.328719944701972</v>
+        <v>1.479700506583936</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5616136643892923</v>
+        <v>0.687716411155266</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.02787135267511</v>
+        <v>3.204072463910268</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.761193386363709</v>
+        <v>2.861732849539283</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.455453675250731</v>
+        <v>-3.329350928484757</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.37865549194967</v>
+        <v>1.529636053831633</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5107269517030978</v>
+        <v>0.6368296984690716</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.067629557385569</v>
+        <v>3.243830668620726</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.775821122479753</v>
+        <v>2.876360585655327</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.553194219875706</v>
+        <v>-3.427091473109732</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.354187010215724</v>
+        <v>1.505167572097687</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4948376735701175</v>
+        <v>0.6209404203360913</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.072723726621824</v>
+        <v>3.248924837856982</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.774357103304425</v>
+        <v>2.874896566479999</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.61340351788099</v>
+        <v>-3.487300771115016</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.328639271838282</v>
+        <v>1.479619833720245</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.434628375564833</v>
+        <v>0.5607311223308068</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.035134128643325</v>
+        <v>3.211335239878483</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.772848721344353</v>
+        <v>2.873388184519927</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.536981471449063</v>
+        <v>-3.410878724683089</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.357699708450981</v>
+        <v>1.508680270332944</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.434628375564833</v>
+        <v>0.5607311223308068</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.033625746683254</v>
+        <v>3.209826857918411</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.77271158877979</v>
+        <v>2.873251051955363</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.492608339810495</v>
+        <v>-3.366505593044521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.375311828541844</v>
+        <v>1.526292390423808</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4790015072034016</v>
+        <v>0.6051042539693754</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.060112493101831</v>
+        <v>3.236313604336989</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.76710538291838</v>
+        <v>2.867644846093954</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.369774118923327</v>
+        <v>-3.243671372157353</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.418839311035302</v>
+        <v>1.569819872917265</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4790015072034016</v>
+        <v>0.6051042539693754</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.054506287240421</v>
+        <v>3.230707398475579</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.773487139946185</v>
+        <v>2.874026603121759</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.322118388362272</v>
+        <v>-3.196015641596298</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.444283360287529</v>
+        <v>1.595263922169492</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5266572377644573</v>
+        <v>0.652759984530431</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.089481482604859</v>
+        <v>3.265682593840018</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.778379513320909</v>
+        <v>2.878918976496483</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.221600229863517</v>
+        <v>-3.095497483097543</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.489382997061755</v>
+        <v>1.640363558943719</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6271753962632118</v>
+        <v>0.7532781430291856</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.154684751078837</v>
+        <v>3.330885862313995</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.765134185796782</v>
+        <v>2.865673648972356</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.282266820265906</v>
+        <v>-3.156164073499932</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.451871033376672</v>
+        <v>1.602851595258635</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5454770795446782</v>
+        <v>0.6715798263106519</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.092420433523589</v>
+        <v>3.268621544758747</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.76923188840741</v>
+        <v>2.869771351582984</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.237428418657508</v>
+        <v>-3.111325671891534</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.47390409663066</v>
+        <v>1.624884658512623</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5500205124895476</v>
+        <v>0.6761232592555214</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.099244195901139</v>
+        <v>3.275445307136297</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.773392828038488</v>
+        <v>2.873932291214062</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.256926874899516</v>
+        <v>-3.130824128133542</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.470265653764935</v>
+        <v>1.621246215646898</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5019358712096433</v>
+        <v>0.6280386179756171</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.074554350764275</v>
+        <v>3.250755461999433</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.779272430566325</v>
+        <v>2.879811893741899</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.212724037813616</v>
+        <v>-3.086621291047642</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.493826391127132</v>
+        <v>1.644806953009095</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5461387082955438</v>
+        <v>0.6722414550615176</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.106955655543652</v>
+        <v>3.28315676677881</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.777682431035573</v>
+        <v>2.878221894211147</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.249703065477059</v>
+        <v>-3.123600318711085</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.477444780531002</v>
+        <v>1.628425342412966</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5831126100868743</v>
+        <v>0.7092153568528481</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.127549997087698</v>
+        <v>3.303751108322856</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.828930196218613</v>
+        <v>2.929469659394186</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.091411647937787</v>
+        <v>-2.965308901171813</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.592009112729751</v>
+        <v>1.742989674611714</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5831126100868743</v>
+        <v>0.7092153568528481</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.178797762270738</v>
+        <v>3.354998873505896</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.827370900812866</v>
+        <v>2.92791036398844</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.883769644303311</v>
+        <v>-2.757666897537337</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.673506618777794</v>
+        <v>1.824487180659758</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7907546137213505</v>
+        <v>0.9168573604873242</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.301823669045676</v>
+        <v>3.478024780280834</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.822319129051136</v>
+        <v>2.92285859222671</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.832737551580783</v>
+        <v>-2.706634804814809</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.688867684105076</v>
+        <v>1.839848245987039</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8417867064438784</v>
+        <v>0.9678894532098522</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.327391152917463</v>
+        <v>3.503592264152621</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.839506533143841</v>
+        <v>2.940045996319415</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.767513370453577</v>
+        <v>-2.641410623687603</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.732144760648663</v>
+        <v>1.883125322530626</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9070108875710841</v>
+        <v>1.033113634337058</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.383713065686492</v>
+        <v>3.559914176921649</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.835467505443121</v>
+        <v>2.936006968618695</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.730086350382444</v>
+        <v>-2.60398360361647</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.743076540976396</v>
+        <v>1.89405710285836</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9122624256002657</v>
+        <v>1.038365172366239</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.382824960803281</v>
+        <v>3.559026072038439</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.836724297774361</v>
+        <v>2.937263760949935</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.750198006417152</v>
+        <v>-2.624095259651178</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.736288670893753</v>
+        <v>1.887269232775717</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9232897705976849</v>
+        <v>1.049392517363658</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.390698160132973</v>
+        <v>3.56689927136813</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.997282068795572</v>
+        <v>3.097821531971146</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.696453191989947</v>
+        <v>-2.570350445223973</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.918344367685846</v>
+        <v>2.069324929567809</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9333530800381469</v>
+        <v>1.059455826804121</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.557293916818461</v>
+        <v>3.733495028053619</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.117394978013389</v>
+        <v>3.217934441188963</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.621670930964934</v>
+        <v>-2.495568184198961</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.068370181313668</v>
+        <v>2.219350743195632</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.00813534106316</v>
+        <v>1.134238087829133</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.722276182651286</v>
+        <v>3.898477293886443</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.109102954027248</v>
+        <v>3.209642417202822</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.595586846701126</v>
+        <v>-2.469484099935153</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.07051179103305</v>
+        <v>2.221492352915014</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.00813534106316</v>
+        <v>1.134238087829133</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.713984158665145</v>
+        <v>3.890185269900302</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.107296149611028</v>
+        <v>3.207835612786602</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.51745566585218</v>
+        <v>-2.391352919086206</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.099957458956409</v>
+        <v>2.250938020838372</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.082312151946844</v>
+        <v>1.208414898712818</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.756683440779135</v>
+        <v>3.932884552014293</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.124850555337819</v>
+        <v>3.225390018513393</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.508563204458897</v>
+        <v>-2.382460457692923</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.121068849240513</v>
+        <v>2.272049411122476</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.082312151946844</v>
+        <v>1.208414898712818</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.774237846505926</v>
+        <v>3.950438957741084</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.116705602742403</v>
+        <v>3.217245065917977</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.677039321428774</v>
+        <v>-2.550936574662801</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.045533449857146</v>
+        <v>2.19651401173911</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.054364316230264</v>
+        <v>1.180467062996237</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.749324192480562</v>
+        <v>3.92552530371572</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.097975299930265</v>
+        <v>3.198514763105839</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.979239792567191</v>
+        <v>-1.853137045801217</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.305922958589641</v>
+        <v>2.456903520471605</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9840162568598529</v>
+        <v>1.110119003625826</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.688385054046177</v>
+        <v>3.864586165281335</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.08863932242717</v>
+        <v>3.189178785602743</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.956518688884039</v>
+        <v>-1.830415942118065</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.305675422559807</v>
+        <v>2.45665598444177</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9840162568598529</v>
+        <v>1.110119003625826</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.679049076543082</v>
+        <v>3.855250187778239</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.247545448278339</v>
+        <v>3.348084911453912</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.085720502178081</v>
+        <v>-1.959617755412107</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.412900823093359</v>
+        <v>2.563881384975322</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8548144435658107</v>
+        <v>0.9809171903317842</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.760434114417825</v>
+        <v>3.936635225652983</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.284623270771985</v>
+        <v>3.385162733947559</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.240501508956337</v>
+        <v>-2.114398762190362</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.388066242875703</v>
+        <v>2.539046804757667</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8214467695113346</v>
+        <v>0.947549516277308</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.777491332478786</v>
+        <v>3.953692443713944</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799966</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.28129862676153</v>
+        <v>3.381838089937104</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.233446818741163</v>
+        <v>-2.107344071975189</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.387563474951318</v>
+        <v>2.538544036833281</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8285014597265083</v>
+        <v>0.9546042064924818</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.778399502597436</v>
+        <v>3.954600613832594</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.291304780406272</v>
+        <v>3.391844243581846</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.206495594414675</v>
+        <v>-2.080392847648701</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.408350118326655</v>
+        <v>2.559330680208618</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8433818057542275</v>
+        <v>0.9694845525202009</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.797333863858809</v>
+        <v>3.973534975093966</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.475407912551232</v>
+        <v>3.575947375726805</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.342448602470991</v>
+        <v>-2.216345855705017</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.538072047249088</v>
+        <v>2.689052609131052</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8433818057542275</v>
+        <v>0.9694845525202009</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.981436996003769</v>
+        <v>4.157638107238927</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.467524607454225</v>
+        <v>3.568064070629799</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.364856720275863</v>
+        <v>-2.238753973509889</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.521225495030132</v>
+        <v>2.672206056912096</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8433818057542275</v>
+        <v>0.9694845525202009</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.973553690906762</v>
+        <v>4.14975480214192</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.469578607003862</v>
+        <v>3.570118070179436</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.512862487755263</v>
+        <v>-2.386759740989288</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.46407718758801</v>
+        <v>2.615057749469973</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.756654796890686</v>
+        <v>0.8827575436566595</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.923571485138274</v>
+        <v>4.099772596373432</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.525832324725709</v>
+        <v>3.626371787901283</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.522303413643793</v>
+        <v>-2.396200666877818</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.516554534954445</v>
+        <v>2.667535096836409</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8790819144340775</v>
+        <v>1.005184661200051</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.053281473386156</v>
+        <v>4.229482584621314</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.52872341927101</v>
+        <v>3.629262882446584</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.574577020979434</v>
+        <v>-2.44847427421346</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.498536186565489</v>
+        <v>2.649516748447453</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8268083070984362</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.024808403530072</v>
+        <v>4.20100951476523</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.526835232164785</v>
+        <v>3.627374695340359</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.65090699858034</v>
+        <v>-2.524804251814365</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.466116008418902</v>
+        <v>2.617096570300866</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8268083070984362</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.022920216423847</v>
+        <v>4.199121327659006</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.521655461767648</v>
+        <v>3.622194924943221</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.762663951195641</v>
+        <v>-2.636561204429666</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.416233456975644</v>
+        <v>2.567214018857608</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7150513544831352</v>
+        <v>0.8411541012491086</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.950686274457529</v>
+        <v>4.126887385692687</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.5200894719778</v>
+        <v>3.620628935153374</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.76082293213739</v>
+        <v>-2.634720185371415</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.415403874809097</v>
+        <v>2.56638443669106</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7163195811546036</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.949881220670562</v>
+        <v>4.12608233190572</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647106</v>
+        <v>3.754911907647108</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.533162878843719</v>
+        <v>3.633702342019292</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.893124224234943</v>
+        <v>-2.767021477468969</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.375556764835994</v>
+        <v>2.526537326717958</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7163195811546036</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.962954627536481</v>
+        <v>4.139155738771639</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763535</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.533162878843719</v>
+        <v>3.633702342019292</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.894685867049803</v>
+        <v>-2.768583120283829</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.37493210771005</v>
+        <v>2.525912669592014</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7163195811546036</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.962954627536481</v>
+        <v>4.139155738771639</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392119</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.531686919970721</v>
+        <v>3.632226383146294</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.922586654159276</v>
+        <v>-2.796483907393302</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.362295833993262</v>
+        <v>2.513276395875226</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6817226570116688</v>
+        <v>0.8078254037776422</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.940720514177722</v>
+        <v>4.11692162541288</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172529</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.528451363947919</v>
+        <v>3.628990827123493</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.04511275686217</v>
+        <v>-2.919010010096196</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.310049836889304</v>
+        <v>2.461030398771268</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5591965543087749</v>
+        <v>0.6852993010747483</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.863969296533185</v>
+        <v>4.040170407768342</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.595157323538423</v>
+        <v>3.695696786713997</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.065174078138677</v>
+        <v>-2.939071331372702</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.368731267969205</v>
+        <v>2.519711829851169</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5391352330322678</v>
+        <v>0.6652379797982413</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.918638463357784</v>
+        <v>4.094839574592942</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199806</v>
+        <v>3.640764248199808</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.73546904254027</v>
+        <v>3.836008505715844</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.321894896133501</v>
+        <v>-3.195792149367526</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.406354659773123</v>
+        <v>2.557335221655086</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.993901437873342</v>
+        <v>4.1701025491085</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.80444931168591</v>
+        <v>3.904988774861484</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.475881313909642</v>
+        <v>-3.349778567143667</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.413740361808306</v>
+        <v>2.564720923690269</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.062881707018982</v>
+        <v>4.23908281825414</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.790500513806031</v>
+        <v>3.891039976981605</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.425359410081976</v>
+        <v>-3.299256663316001</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.420000325459493</v>
+        <v>2.570980887341457</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.048932909139102</v>
+        <v>4.225134020374261</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.802371002861445</v>
+        <v>3.902910466037019</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.6778345640897</v>
+        <v>-3.551731817323725</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.330880752911817</v>
+        <v>2.481861314793781</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.060803398194517</v>
+        <v>4.237004509429675</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.6740426963583</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.803581537380389</v>
+        <v>3.904121000555962</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.947307366011408</v>
+        <v>-3.821204619245433</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.224302166662078</v>
+        <v>2.375282728544041</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.062013932713461</v>
+        <v>4.238215043948618</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637089</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.80770327960771</v>
+        <v>3.908242742783284</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.10485143774085</v>
+        <v>-3.978748690974875</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.165406280197623</v>
+        <v>2.316386842079587</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3638188537481785</v>
+        <v>0.489921600514152</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.025994591856617</v>
+        <v>4.202195703091776</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301344</v>
+        <v>3.652163313301346</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.802781132343899</v>
+        <v>3.903320595519473</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.382815833324123</v>
+        <v>-4.256713086558149</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.049298374700503</v>
+        <v>2.200278936582467</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2741991194626943</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.967300604021516</v>
+        <v>4.143501715256674</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66797646721547</v>
+        <v>3.667976467215472</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.964985189042944</v>
+        <v>4.065524652218517</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.499783525963014</v>
+        <v>-4.37368077919704</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.164715354343991</v>
+        <v>2.315695916225954</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2741991194626943</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.12950466072056</v>
+        <v>4.305705771955719</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.696553628456694</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.959831827006758</v>
+        <v>4.060371290182331</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.584501468183968</v>
+        <v>-4.458398721417993</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.125674815419424</v>
+        <v>2.276655377301387</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1890830905346479</v>
+        <v>0.3151858373006214</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.073281681327547</v>
+        <v>4.249482792562705</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253289</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.970061244575249</v>
+        <v>4.070600707750823</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.666436286452851</v>
+        <v>-4.540333539686876</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.103130305680362</v>
+        <v>2.254110867562325</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1791483449475677</v>
+        <v>0.3052510917135412</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.07755025154379</v>
+        <v>4.253751362778948</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717834</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.978986883031151</v>
+        <v>4.079526346206725</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.612698113052589</v>
+        <v>-4.486595366286614</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.133551213496369</v>
+        <v>2.284531775378333</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2328865183478298</v>
+        <v>0.3589892651138033</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.118718794039849</v>
+        <v>4.294919905275007</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616949</v>
+        <v>3.798310944616951</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.971139770275327</v>
+        <v>4.071679233450901</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.502691829575367</v>
+        <v>-4.376589082809392</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.169706614131433</v>
+        <v>2.320687176013397</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.256091090265105</v>
+        <v>0.3821938370310785</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.12479442443439</v>
+        <v>4.300995535669548</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203664</v>
+        <v>3.785578085203666</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.975389780997301</v>
+        <v>4.075929244172875</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.359632253834441</v>
+        <v>-4.233529507068466</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.231180455149778</v>
+        <v>2.382161017031741</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2641045168550843</v>
+        <v>0.3902072636210578</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.133852491110352</v>
+        <v>4.31005360234551</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436931</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.982650663879838</v>
+        <v>4.083190127055412</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.058185528362603</v>
+        <v>-3.932082781596629</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.359020028221049</v>
+        <v>2.510000590103012</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5655512423269216</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.321981409275991</v>
+        <v>4.498182520511149</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064767</v>
+        <v>3.812650101064769</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.983621841632548</v>
+        <v>4.084161304808122</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.113140724805673</v>
+        <v>-3.987037978039698</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.338009127396532</v>
+        <v>2.488989689278495</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5655512423269216</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.322952587028701</v>
+        <v>4.499153698263859</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.821198342859303</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.984464746012303</v>
+        <v>4.085004209187877</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.062102348799153</v>
+        <v>-3.935999602033178</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.359267382178895</v>
+        <v>2.510247944060859</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5655512423269216</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.323795491408457</v>
+        <v>4.499996602643614</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354686</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.003502844886449</v>
+        <v>4.104042308062023</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.020963053932522</v>
+        <v>-3.894860307166547</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.394761198999693</v>
+        <v>2.545741760881657</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6066905371935524</v>
+        <v>0.7327932839595258</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.367517167202581</v>
+        <v>4.543718278437739</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82576709308562</v>
+        <v>3.825767093085622</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.819686841010383</v>
+        <v>3.920226304185957</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.91035691385292</v>
+        <v>-3.784254167086945</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.255187651155468</v>
+        <v>2.406168213037431</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7172966772731544</v>
+        <v>0.8433994240391278</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.250064847374277</v>
+        <v>4.426265958609434</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.594656226348546</v>
+        <v>3.806352498007638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.823188885084347</v>
+        <v>3.923728348259921</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.925512563074596</v>
+        <v>-3.914834901617787</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.252627435540761</v>
+        <v>2.357437963299059</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7021410280514778</v>
+        <v>0.7128186895082853</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.244473501915234</v>
+        <v>4.351419561964892</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.1%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.1%</t>
+          <t>-556.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-46.7%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-140.5%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.7%</t>
+          <t>-128.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-150.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-19.6%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.92281506170616</v>
+        <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
         <v>-3.542552412239842</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.505437672496476</v>
+        <v>1.404898209320902</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4896982189861117</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.216633993097827</v>
+        <v>3.116094529922254</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.989150615502981</v>
+        <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.480254413463721</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.596692425803746</v>
+        <v>1.496152962628172</v>
       </c>
       <c r="F1970" t="n">
         <v>0.4896982189861117</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.282969546894648</v>
+        <v>3.182430083719074</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.791442617217108</v>
+        <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.278464215798563</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.479700506583936</v>
+        <v>1.379161043408362</v>
       </c>
       <c r="F1971" t="n">
         <v>0.687716411155266</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.204072463910268</v>
+        <v>3.103533000734694</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.861732849539283</v>
+        <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.329350928484757</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.529636053831633</v>
+        <v>1.429096590656059</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6368296984690716</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.243830668620726</v>
+        <v>3.143291205445153</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.876360585655327</v>
+        <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.427091473109732</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.505167572097687</v>
+        <v>1.404628108922113</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6209404203360913</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.248924837856982</v>
+        <v>3.148385374681408</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.874896566479999</v>
+        <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.487300771115016</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.479619833720245</v>
+        <v>1.379080370544671</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5607311223308068</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.211335239878483</v>
+        <v>3.110795776702909</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.873388184519927</v>
+        <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.410878724683089</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.508680270332944</v>
+        <v>1.40814080715737</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5607311223308068</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.209826857918411</v>
+        <v>3.109287394742838</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.873251051955363</v>
+        <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.366505593044521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.526292390423808</v>
+        <v>1.425752927248234</v>
       </c>
       <c r="F1976" t="n">
         <v>0.6051042539693754</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.236313604336989</v>
+        <v>3.135774141161415</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.867644846093954</v>
+        <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.243671372157353</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.569819872917265</v>
+        <v>1.469280409741691</v>
       </c>
       <c r="F1977" t="n">
         <v>0.6051042539693754</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.230707398475579</v>
+        <v>3.130167935300006</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.874026603121759</v>
+        <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.196015641596298</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.595263922169492</v>
+        <v>1.494724458993918</v>
       </c>
       <c r="F1978" t="n">
         <v>0.652759984530431</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.265682593840018</v>
+        <v>3.165143130664444</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.878918976496483</v>
+        <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.095497483097543</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.640363558943719</v>
+        <v>1.539824095768145</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7532781430291856</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.330885862313995</v>
+        <v>3.230346399138421</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.865673648972356</v>
+        <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.156164073499932</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.602851595258635</v>
+        <v>1.502312132083061</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6715798263106519</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.268621544758747</v>
+        <v>3.168082081583173</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.869771351582984</v>
+        <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.111325671891534</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.624884658512623</v>
+        <v>1.524345195337049</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6761232592555214</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.275445307136297</v>
+        <v>3.174905843960723</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.873932291214062</v>
+        <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.130824128133542</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.621246215646898</v>
+        <v>1.520706752471324</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6280386179756171</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.250755461999433</v>
+        <v>3.150215998823859</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.879811893741899</v>
+        <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.086621291047642</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.644806953009095</v>
+        <v>1.544267489833521</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6722414550615176</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.28315676677881</v>
+        <v>3.182617303603236</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.878221894211147</v>
+        <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.123600318711085</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.628425342412966</v>
+        <v>1.527885879237392</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7092153568528481</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.303751108322856</v>
+        <v>3.203211645147282</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.929469659394186</v>
+        <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
         <v>-2.965308901171813</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.742989674611714</v>
+        <v>1.64245021143614</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7092153568528481</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.354998873505896</v>
+        <v>3.254459410330322</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.92791036398844</v>
+        <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
         <v>-2.757666897537337</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.824487180659758</v>
+        <v>1.723947717484184</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9168573604873242</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.478024780280834</v>
+        <v>3.37748531710526</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.92285859222671</v>
+        <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
         <v>-2.706634804814809</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.839848245987039</v>
+        <v>1.739308782811465</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9678894532098522</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.503592264152621</v>
+        <v>3.403052800977047</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.940045996319415</v>
+        <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.641410623687603</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.883125322530626</v>
+        <v>1.782585859355052</v>
       </c>
       <c r="F1988" t="n">
         <v>1.033113634337058</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.559914176921649</v>
+        <v>3.459374713746076</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.936006968618695</v>
+        <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.60398360361647</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.89405710285836</v>
+        <v>1.793517639682786</v>
       </c>
       <c r="F1989" t="n">
         <v>1.038365172366239</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.559026072038439</v>
+        <v>3.458486608862865</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.937263760949935</v>
+        <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
         <v>-2.624095259651178</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.887269232775717</v>
+        <v>1.786729769600143</v>
       </c>
       <c r="F1990" t="n">
         <v>1.049392517363658</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.56689927136813</v>
+        <v>3.466359808192557</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.097821531971146</v>
+        <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
         <v>-2.570350445223973</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.069324929567809</v>
+        <v>1.968785466392236</v>
       </c>
       <c r="F1991" t="n">
         <v>1.059455826804121</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.733495028053619</v>
+        <v>3.632955564878045</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.217934441188963</v>
+        <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.495568184198961</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.219350743195632</v>
+        <v>2.118811280020058</v>
       </c>
       <c r="F1992" t="n">
         <v>1.134238087829133</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.898477293886443</v>
+        <v>3.79793783071087</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.209642417202822</v>
+        <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.469484099935153</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.221492352915014</v>
+        <v>2.12095288973944</v>
       </c>
       <c r="F1993" t="n">
         <v>1.134238087829133</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.890185269900302</v>
+        <v>3.789645806724729</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.207835612786602</v>
+        <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.391352919086206</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.250938020838372</v>
+        <v>2.150398557662798</v>
       </c>
       <c r="F1994" t="n">
         <v>1.208414898712818</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.932884552014293</v>
+        <v>3.832345088838719</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.225390018513393</v>
+        <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.382460457692923</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.272049411122476</v>
+        <v>2.171509947946903</v>
       </c>
       <c r="F1995" t="n">
         <v>1.208414898712818</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.950438957741084</v>
+        <v>3.84989949456551</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.217245065917977</v>
+        <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.550936574662801</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.19651401173911</v>
+        <v>2.095974548563536</v>
       </c>
       <c r="F1996" t="n">
         <v>1.180467062996237</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.92552530371572</v>
+        <v>3.824985840540146</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.198514763105839</v>
+        <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
         <v>-1.853137045801217</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.456903520471605</v>
+        <v>2.356364057296031</v>
       </c>
       <c r="F1997" t="n">
         <v>1.110119003625826</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.864586165281335</v>
+        <v>3.764046702105761</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.189178785602743</v>
+        <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
         <v>-1.830415942118065</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.45665598444177</v>
+        <v>2.356116521266197</v>
       </c>
       <c r="F1998" t="n">
         <v>1.110119003625826</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.855250187778239</v>
+        <v>3.754710724602666</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.348084911453912</v>
+        <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
         <v>-1.959617755412107</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.563881384975322</v>
+        <v>2.463341921799748</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9809171903317842</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.936635225652983</v>
+        <v>3.836095762477409</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.385162733947559</v>
+        <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.114398762190362</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.539046804757667</v>
+        <v>2.438507341582093</v>
       </c>
       <c r="F2000" t="n">
         <v>0.947549516277308</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.953692443713944</v>
+        <v>3.85315298053837</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799966</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.381838089937104</v>
+        <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.107344071975189</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.538544036833281</v>
+        <v>2.438004573657707</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9546042064924818</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.954600613832594</v>
+        <v>3.854061150657019</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.391844243581846</v>
+        <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.080392847648701</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.559330680208618</v>
+        <v>2.458791217033044</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9694845525202009</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.973534975093966</v>
+        <v>3.872995511918393</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.575947375726805</v>
+        <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.216345855705017</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.689052609131052</v>
+        <v>2.588513145955478</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9694845525202009</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.157638107238927</v>
+        <v>4.057098644063353</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.568064070629799</v>
+        <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.238753973509889</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.672206056912096</v>
+        <v>2.571666593736522</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9694845525202009</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.14975480214192</v>
+        <v>4.049215338966346</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.570118070179436</v>
+        <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.386759740989288</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.615057749469973</v>
+        <v>2.5145182862944</v>
       </c>
       <c r="F2005" t="n">
         <v>0.8827575436566595</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.099772596373432</v>
+        <v>3.999233133197858</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.626371787901283</v>
+        <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.396200666877818</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.667535096836409</v>
+        <v>2.566995633660835</v>
       </c>
       <c r="F2006" t="n">
         <v>1.005184661200051</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.229482584621314</v>
+        <v>4.12894312144574</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.629262882446584</v>
+        <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.44847427421346</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.649516748447453</v>
+        <v>2.548977285271879</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9529110538644098</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.20100951476523</v>
+        <v>4.100470051589657</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.627374695340359</v>
+        <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.524804251814365</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.617096570300866</v>
+        <v>2.516557107125292</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9529110538644098</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.199121327659006</v>
+        <v>4.098581864483432</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.622194924943221</v>
+        <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
         <v>-2.636561204429666</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.567214018857608</v>
+        <v>2.466674555682034</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8411541012491086</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.126887385692687</v>
+        <v>4.026347922517113</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.620628935153374</v>
+        <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
         <v>-2.634720185371415</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.56638443669106</v>
+        <v>2.465844973515487</v>
       </c>
       <c r="F2010" t="n">
         <v>0.842422327920577</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.12608233190572</v>
+        <v>4.025542868730146</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647108</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.633702342019292</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
         <v>-2.767021477468969</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.526537326717958</v>
+        <v>2.425997863542384</v>
       </c>
       <c r="F2011" t="n">
         <v>0.842422327920577</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.139155738771639</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763535</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.633702342019292</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
         <v>-2.768583120283829</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.525912669592014</v>
+        <v>2.42537320641644</v>
       </c>
       <c r="F2012" t="n">
         <v>0.842422327920577</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.139155738771639</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392119</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.632226383146294</v>
+        <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
         <v>-2.796483907393302</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.513276395875226</v>
+        <v>2.412736932699652</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8078254037776422</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.11692162541288</v>
+        <v>4.016382162237306</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172529</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.628990827123493</v>
+        <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
         <v>-2.919010010096196</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.461030398771268</v>
+        <v>2.360490935595694</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6852993010747483</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.040170407768342</v>
+        <v>3.939630944592769</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.695696786713997</v>
+        <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
         <v>-2.939071331372702</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.519711829851169</v>
+        <v>2.419172366675595</v>
       </c>
       <c r="F2015" t="n">
         <v>0.6652379797982413</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.094839574592942</v>
+        <v>3.994300111417368</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199808</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.836008505715844</v>
+        <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
         <v>-3.195792149367526</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.557335221655086</v>
+        <v>2.456795758479513</v>
       </c>
       <c r="F2016" t="n">
         <v>0.5568234056544265</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.1701025491085</v>
+        <v>4.069563085932926</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.904988774861484</v>
+        <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
         <v>-3.349778567143667</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.564720923690269</v>
+        <v>2.464181460514696</v>
       </c>
       <c r="F2017" t="n">
         <v>0.5568234056544265</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.23908281825414</v>
+        <v>4.138543355078566</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.891039976981605</v>
+        <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
         <v>-3.299256663316001</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.570980887341457</v>
+        <v>2.470441424165883</v>
       </c>
       <c r="F2018" t="n">
         <v>0.5568234056544265</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.225134020374261</v>
+        <v>4.124594557198687</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994896</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.902910466037019</v>
+        <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
         <v>-3.551731817323725</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.481861314793781</v>
+        <v>2.381321851618207</v>
       </c>
       <c r="F2019" t="n">
         <v>0.5568234056544265</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.237004509429675</v>
+        <v>4.136465046254101</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.6740426963583</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.904121000555962</v>
+        <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
         <v>-3.821204619245433</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.375282728544041</v>
+        <v>2.274743265368468</v>
       </c>
       <c r="F2020" t="n">
         <v>0.5568234056544265</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.238215043948618</v>
+        <v>4.137675580773045</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637089</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.908242742783284</v>
+        <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
         <v>-3.978748690974875</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.316386842079587</v>
+        <v>2.215847378904013</v>
       </c>
       <c r="F2021" t="n">
         <v>0.489921600514152</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.202195703091776</v>
+        <v>4.101656239916202</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301346</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.903320595519473</v>
+        <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
         <v>-4.256713086558149</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.200278936582467</v>
+        <v>2.099739473406893</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4003018662286678</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.143501715256674</v>
+        <v>4.0429622520811</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215472</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
-        <v>4.065524652218517</v>
+        <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
         <v>-4.37368077919704</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.315695916225954</v>
+        <v>2.215156453050381</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4003018662286678</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.305705771955719</v>
+        <v>4.205166308780145</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456694</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
-        <v>4.060371290182331</v>
+        <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.458398721417993</v>
+        <v>-4.496460381166054</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.276655377301387</v>
+        <v>2.160891250226589</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3151858373006214</v>
+        <v>0.3367851668275899</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.249482792562705</v>
+        <v>4.161902927103312</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253289</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
-        <v>4.070600707750823</v>
+        <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.540333539686876</v>
+        <v>-4.578395199434937</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.254110867562325</v>
+        <v>2.138346740487527</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3052510917135412</v>
+        <v>0.3268504212405097</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.253751362778948</v>
+        <v>4.166171497319556</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717834</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
-        <v>4.079526346206725</v>
+        <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.486595366286614</v>
+        <v>-4.524657026034675</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.284531775378333</v>
+        <v>2.168767648303534</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3589892651138033</v>
+        <v>0.3805885946407718</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.294919905275007</v>
+        <v>4.207340039815614</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616951</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
-        <v>4.071679233450901</v>
+        <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.376589082809392</v>
+        <v>-4.414650742557454</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.320687176013397</v>
+        <v>2.204923048938598</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3821938370310785</v>
+        <v>0.403793166558047</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.300995535669548</v>
+        <v>4.213415670210155</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203666</v>
+        <v>3.785578085203663</v>
       </c>
       <c r="C2028" t="n">
-        <v>4.075929244172875</v>
+        <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.233529507068466</v>
+        <v>-4.271591166816528</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.382161017031741</v>
+        <v>2.266396889956943</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3902072636210578</v>
+        <v>0.4118065931480263</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.31005360234551</v>
+        <v>4.222473736886117</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436931</v>
+        <v>3.777251572436929</v>
       </c>
       <c r="C2029" t="n">
-        <v>4.083190127055412</v>
+        <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.932082781596629</v>
+        <v>-3.97014444134469</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.510000590103012</v>
+        <v>2.394236463028214</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.691653989092895</v>
+        <v>0.7132533186198635</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.498182520511149</v>
+        <v>4.410602655051756</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064769</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
-        <v>4.084161304808122</v>
+        <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.987037978039698</v>
+        <v>-4.025099637787759</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.488989689278495</v>
+        <v>2.373225562203697</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.691653989092895</v>
+        <v>0.7132533186198635</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.499153698263859</v>
+        <v>4.411573832804466</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859303</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
-        <v>4.085004209187877</v>
+        <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.935999602033178</v>
+        <v>-3.974061261781239</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.510247944060859</v>
+        <v>2.39448381698606</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.691653989092895</v>
+        <v>0.7132533186198635</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.499996602643614</v>
+        <v>4.412416737184222</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354686</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.104042308062023</v>
+        <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.894860307166547</v>
+        <v>-3.932921966914608</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.545741760881657</v>
+        <v>2.429977633806859</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7327932839595258</v>
+        <v>0.7543926134864943</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.543718278437739</v>
+        <v>4.456138412978346</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085622</v>
+        <v>3.82576709308562</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.920226304185957</v>
+        <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.784254167086945</v>
+        <v>-3.822315826835006</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.406168213037431</v>
+        <v>2.290404085962634</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8433994240391278</v>
+        <v>0.8649987535660963</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.426265958609434</v>
+        <v>4.338686093150042</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.806352498007638</v>
+        <v>3.84171412926164</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.923728348259921</v>
+        <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.914834901617787</v>
+        <v>-3.952896561365849</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.357437963299059</v>
+        <v>2.24167383622426</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.7344180190352538</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.351419561964892</v>
+        <v>4.263839696505499</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>456.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-556.9%</t>
+          <t>-572.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-148.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-128.3%</t>
+          <t>-119.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.6%</t>
+          <t>-163.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2034"/>
+  <dimension ref="A1:G2035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.025279242125166</v>
+        <v>-7.15138198889114</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.34828310299805</v>
+        <v>0.2978420042916605</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-1.003265731997947</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.556791784963096</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.875612851117651</v>
+        <v>-7.001715597883625</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4052574490880967</v>
+        <v>0.3548163503817072</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.9103622407554106</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.609641669395659</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.743337377486765</v>
+        <v>-6.869440124252739</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4535351252874782</v>
+        <v>0.4030940265810887</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.778086767124524</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.684374440321218</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.587599044927023</v>
+        <v>-6.713701791692997</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.518645518999012</v>
+        <v>0.4682044202926221</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6223484345647824</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.780632500544699</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338599246243442</v>
+        <v>-6.464701993009416</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6311517796961028</v>
+        <v>0.5807106809897133</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6223484345647824</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.793538841768358</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.444189236016546</v>
+        <v>-6.57029198278252</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4609398541876426</v>
+        <v>0.4104987554812531</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.7279384243378867</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.602208918305277</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.462924138135143</v>
+        <v>-6.589026884901117</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5019902352172902</v>
+        <v>0.4515491365109003</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.733534433998018</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.647395654386284</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.314984096727544</v>
+        <v>-6.441086843493518</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4412873290921624</v>
+        <v>0.3908462303857725</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.7132135180894604</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.539709281243251</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.262014574473556</v>
+        <v>-6.388117321239529</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4537611517402795</v>
+        <v>0.4033200530338901</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.562777008342167</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.218466167702865</v>
+        <v>-6.344568914468839</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4642199023534626</v>
+        <v>0.4137788036470731</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.555816396247073</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.185102961224096</v>
+        <v>-6.31120570799007</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4920275393261129</v>
+        <v>0.4415864406197234</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.570278750628217</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.076843824101575</v>
+        <v>-6.202946570867549</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5298633146343166</v>
+        <v>0.4794222159279271</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6602439958354716</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.564810871087412</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.953552689284444</v>
+        <v>-6.079655436050418</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5766778625717461</v>
+        <v>0.5262367638653562</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.5369528610183411</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.636283645988267</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.932403490381001</v>
+        <v>-6.058506237146974</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5928385203704485</v>
+        <v>0.542397421664059</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.5158036621148977</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.656674143567658</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.688638048397556</v>
+        <v>-5.81474079516353</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.686125405510877</v>
+        <v>0.6356843068044875</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.5158036621148977</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.652454851914709</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.586875228120261</v>
+        <v>-5.712977974886235</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7289548475418108</v>
+        <v>0.6785137488354214</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.502584593722469</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.662510606870182</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.337024834171187</v>
+        <v>-5.463127580937161</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8216370801051429</v>
+        <v>0.7711959813987534</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.502584593722469</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.655252681853884</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.161132741703755</v>
+        <v>-5.287235488469728</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955930406127646</v>
+        <v>0.8451519419063751</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.502584593722469</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.658851805374533</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.989686278681291</v>
+        <v>-5.115789025447264</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9774991318763036</v>
+        <v>0.9270580331699145</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.3311381307000059</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.775047189242564</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.915396712942952</v>
+        <v>-5.041499459708925</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006235435787936</v>
+        <v>0.9557943370815472</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.2568485649616666</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.818641406301865</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.851760970709018</v>
+        <v>-4.977863717474991</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036384533735827</v>
+        <v>0.985943435029438</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.193212822727732</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.861517652696543</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.740334211383098</v>
+        <v>-4.866436958149071</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.062149496249991</v>
+        <v>1.011708397543602</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.193212822727732</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.842711911480338</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.499903714578237</v>
+        <v>-4.62600646134421</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.160064771596812</v>
+        <v>1.109623672890423</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.04721767407712824</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>2.988713286188132</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.427661146407043</v>
+        <v>-4.553763893173016</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.192891112700111</v>
+        <v>1.142450013993721</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.04721767407712824</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>2.992642600022952</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.409947459529177</v>
+        <v>-4.53605020629515</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.200655171368597</v>
+        <v>1.150214072662207</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.05039900297404504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.070891629338026</v>
+        <v>2.995229981278442</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.30114257404945</v>
+        <v>-4.427245320815423</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.241175196780481</v>
+        <v>1.190734098074092</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.05039900297404504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.06788970055802</v>
+        <v>2.992228052498436</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08112177601244</v>
+        <v>-4.207224522778413</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.330762553005899</v>
+        <v>1.28032145429951</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.1916188480420253</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.154200644609422</v>
+        <v>3.078538996549838</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948254086949162</v>
+        <v>-4.074356833715135</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399803811433034</v>
+        <v>1.349362712726645</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.1916188480420253</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.170094827411245</v>
+        <v>3.094433179351661</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828081003584662</v>
+        <v>-3.954183750350636</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449018889219135</v>
+        <v>1.398577790512746</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.437894678172498</v>
+        <v>0.3117919314065242</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.243344521870247</v>
+        <v>3.167682873810663</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.683408858484925</v>
+        <v>-3.809511605250899</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.51697584982047</v>
+        <v>1.466534751114081</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5825668232722354</v>
+        <v>0.4564640765062616</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.340235911491529</v>
+        <v>3.264574263431945</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.743283685842617</v>
+        <v>-3.869386432608591</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479063410278819</v>
+        <v>1.428622311572429</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.3965892491485695</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.29034850647834</v>
+        <v>3.214686858418755</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.62346345493178</v>
+        <v>-3.749566201697754</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.542280671877363</v>
+        <v>1.491839573170973</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.3965892491485695</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.305637675712548</v>
+        <v>3.229976027652964</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.625933161393586</v>
+        <v>-3.75203590815956</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.448936988615082</v>
+        <v>1.398495889908692</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5202222894527371</v>
+        <v>0.3941195426867634</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.211800051157906</v>
+        <v>3.136138403098322</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.694303347717596</v>
+        <v>-3.82040609448357</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.340850775570779</v>
+        <v>1.29040967686439</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.136627332064936</v>
+        <v>3.060965684005352</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.708091400564642</v>
+        <v>-3.834194147330616</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325772263063852</v>
+        <v>1.275331164357462</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.127064040696828</v>
+        <v>3.051402392637244</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.763611476457232</v>
+        <v>-3.889714223223206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.440595069399018</v>
+        <v>1.390153970692629</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.26409487738903</v>
+        <v>3.188433229329446</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.588137216664763</v>
+        <v>-3.714239963430737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.515352005307794</v>
+        <v>1.464910906601404</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.268662109380818</v>
+        <v>3.193000461321234</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.699073469306011</v>
+        <v>-3.825176216071985</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.446719533012502</v>
+        <v>1.396278434306112</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4033952417229783</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.244404138142025</v>
+        <v>3.168742490082441</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.665409923833729</v>
+        <v>-3.791512670599703</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.388723264602864</v>
+        <v>1.338282165896475</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4370587871952601</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.193140578826844</v>
+        <v>3.117478930767259</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.605557304630006</v>
+        <v>-3.73166005139598</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.422836698716486</v>
+        <v>1.372395600010096</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4370587871952601</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.203312965258976</v>
+        <v>3.127651317199392</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.519313841603629</v>
+        <v>-3.645416588369603</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.452280354500897</v>
+        <v>1.401839255794507</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4370587871952601</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.198259235832837</v>
+        <v>3.122597587773252</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.564620661002609</v>
+        <v>-3.690723407768583</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.425933402185831</v>
+        <v>1.375492303479441</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.3962486241860294</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.165548913471823</v>
+        <v>3.089887265412239</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.59365376570491</v>
+        <v>-3.719756512470884</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.414872033338011</v>
+        <v>1.364430934631622</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.3962486241860294</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.166100786504925</v>
+        <v>3.090439138445341</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.500843284254051</v>
+        <v>-3.626946031020025</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.381268917809721</v>
+        <v>1.330827819103331</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6151618524028625</v>
+        <v>0.4890591056368887</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.151059767266806</v>
+        <v>3.075398119207222</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.545232753583479</v>
+        <v>-3.671335500349453</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.365386606002551</v>
+        <v>1.314945507296161</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5707723830734348</v>
+        <v>0.444669636307461</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.126299561593751</v>
+        <v>3.050637913534166</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.432561535347229</v>
+        <v>-3.558664282113202</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.405530801808774</v>
+        <v>1.355089703102384</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.683443601309685</v>
+        <v>0.5573408545437112</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.188978001047224</v>
+        <v>3.113316352987639</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.320184534164556</v>
+        <v>-3.44628728093053</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.45597289811251</v>
+        <v>1.40553179940612</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.683443601309685</v>
+        <v>0.5573408545437112</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.194469296877891</v>
+        <v>3.118807648818307</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.347964932065909</v>
+        <v>-3.474067678831883</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.456357940720508</v>
+        <v>1.405916842014118</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6556632034083318</v>
+        <v>0.5295604566423581</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.189298259905618</v>
+        <v>3.113636611846034</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.466345604796047</v>
+        <v>-3.592448351562021</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.247361391629106</v>
+        <v>1.196920292922716</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4623426044913819</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.987323268615686</v>
+        <v>2.911661620556101</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.574959683239379</v>
+        <v>-3.701062430005353</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.324065420970979</v>
+        <v>1.273624322264589</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4623426044913819</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.107472929334891</v>
+        <v>3.031811281275307</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.539550644991236</v>
+        <v>-3.66565339175721</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.352742062372559</v>
+        <v>1.302300963666169</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4623426044913819</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.121985955437214</v>
+        <v>3.04632430737763</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.501166982433085</v>
+        <v>-3.627269729199059</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.365514968738188</v>
+        <v>1.315073870031799</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.500726267049533</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.142435594314474</v>
+        <v>3.06677394625489</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.324050652397919</v>
+        <v>-3.450153399163892</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.433090529597556</v>
+        <v>1.382649430891167</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.500726267049533</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.139164623159775</v>
+        <v>3.063502975100191</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.369142897231464</v>
+        <v>-3.495245643997438</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.415737023426051</v>
+        <v>1.365295924719662</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.564932970646117</v>
+        <v>0.4388302238801433</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.102710389020055</v>
+        <v>3.02704874096047</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.189767475992697</v>
+        <v>-3.31587022275867</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.481274167227973</v>
+        <v>1.430833068521583</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7217097288168357</v>
+        <v>0.5956069820508619</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.190563419228901</v>
+        <v>3.114901771169316</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.234781689513303</v>
+        <v>-3.360884436279277</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.44407593715132</v>
+        <v>1.39363483844493</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6913608335022311</v>
+        <v>0.5652580867362573</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.153161537371727</v>
+        <v>3.077499889312143</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.501786199785738</v>
+        <v>-3.627888946551712</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.342965695381292</v>
+        <v>1.292524596674902</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4969977954592826</v>
+        <v>0.3708950486933087</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.042235276884904</v>
+        <v>2.96657362882532</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.602983981222911</v>
+        <v>-3.729086727988885</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.301690504702924</v>
+        <v>1.251249405996534</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.3024862351479896</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.000393910654214</v>
+        <v>2.92473226259463</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.596473014608598</v>
+        <v>-3.722575761374572</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.301894852902966</v>
+        <v>1.251453754196576</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.3024862351479896</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.99799387220853</v>
+        <v>2.922332224148946</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.577434886901301</v>
+        <v>-3.703537633667275</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.306034823194129</v>
+        <v>1.25559372448774</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.244302623816795</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.959608424618059</v>
+        <v>2.883946776558474</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.608561518051919</v>
+        <v>-3.734664264817893</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.471166039672563</v>
+        <v>1.420724940966173</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.244302623816795</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.137190293556739</v>
+        <v>3.061528645497155</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.622428279385836</v>
+        <v>-3.74853102615181</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.466452664125129</v>
+        <v>1.41601156541874</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.2064447070829721</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.115308872502579</v>
+        <v>3.039647224442995</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.577624107845907</v>
+        <v>-3.70372685461188</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.490382863138027</v>
+        <v>1.439941764431638</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.2064447070829721</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.121317402899505</v>
+        <v>3.045655754839921</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.429881137610904</v>
+        <v>-3.555983884376878</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.447430272509228</v>
+        <v>1.396989173802838</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.3742520643178552</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.119952038517634</v>
+        <v>3.04429039045805</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.531895820142125</v>
+        <v>-3.657998566908099</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.40941802102822</v>
+        <v>1.358976922321831</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.3742520643178552</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.122745660049115</v>
+        <v>3.047084011989531</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.525743114089341</v>
+        <v>-3.651845860855315</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.412541451840992</v>
+        <v>1.362100353134603</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5065075171366133</v>
+        <v>0.3804047703706395</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.127099632072444</v>
+        <v>3.05143798401286</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.822275598530586</v>
+        <v>2.918582727259874</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.542552412239842</v>
+        <v>-3.668655159005816</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.404898209320902</v>
+        <v>1.4507642393438</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.3635954722201379</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.116094529922254</v>
+        <v>3.136740010591957</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.888611152327407</v>
+        <v>2.984918281056695</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.480254413463721</v>
+        <v>-3.606357160229694</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.496152962628172</v>
+        <v>1.54201899265107</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.3635954722201379</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182430083719074</v>
+        <v>3.203075564388778</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.690903154041534</v>
+        <v>2.787210282770822</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.278464215798563</v>
+        <v>-3.404566962564537</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.379161043408362</v>
+        <v>1.42502707343126</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.687716411155266</v>
+        <v>0.5616136643892923</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.103533000734694</v>
+        <v>3.124178481404398</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.761193386363709</v>
+        <v>2.857500515092998</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.329350928484757</v>
+        <v>-3.455453675250731</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.429096590656059</v>
+        <v>1.474962620678958</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6368296984690716</v>
+        <v>0.5107269517030978</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143291205445153</v>
+        <v>3.163936686114857</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.775821122479753</v>
+        <v>2.872128251209041</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.427091473109732</v>
+        <v>-3.553194219875706</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.404628108922113</v>
+        <v>1.450494138945012</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6209404203360913</v>
+        <v>0.4948376735701175</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.148385374681408</v>
+        <v>3.169030855351112</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.774357103304425</v>
+        <v>2.870664232033713</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.487300771115016</v>
+        <v>-3.61340351788099</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.379080370544671</v>
+        <v>1.42494640056757</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5607311223308068</v>
+        <v>0.434628375564833</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.110795776702909</v>
+        <v>3.131441257372613</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.772848721344353</v>
+        <v>2.869155850073641</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.410878724683089</v>
+        <v>-3.536981471449063</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.40814080715737</v>
+        <v>1.454006837180269</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5607311223308068</v>
+        <v>0.434628375564833</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.109287394742838</v>
+        <v>3.129932875412542</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.77271158877979</v>
+        <v>2.869018717509078</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.366505593044521</v>
+        <v>-3.492608339810495</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.425752927248234</v>
+        <v>1.471618957271132</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6051042539693754</v>
+        <v>0.4790015072034016</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.135774141161415</v>
+        <v>3.156419621831119</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.76710538291838</v>
+        <v>2.863412511647668</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.243671372157353</v>
+        <v>-3.369774118923327</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.469280409741691</v>
+        <v>1.51514643976459</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6051042539693754</v>
+        <v>0.4790015072034016</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.130167935300006</v>
+        <v>3.150813415969709</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.773487139946185</v>
+        <v>2.869794268675473</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.196015641596298</v>
+        <v>-3.322118388362272</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.494724458993918</v>
+        <v>1.540590489016817</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.652759984530431</v>
+        <v>0.5266572377644573</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.165143130664444</v>
+        <v>3.185788611334147</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.778379513320909</v>
+        <v>2.874686642050198</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.095497483097543</v>
+        <v>-3.221600229863517</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.539824095768145</v>
+        <v>1.585690125791043</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7532781430291856</v>
+        <v>0.6271753962632118</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.230346399138421</v>
+        <v>3.250991879808125</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.765134185796782</v>
+        <v>2.86144131452607</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.156164073499932</v>
+        <v>-3.282266820265906</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.502312132083061</v>
+        <v>1.54817816210596</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6715798263106519</v>
+        <v>0.5454770795446782</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.168082081583173</v>
+        <v>3.188727562252877</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.76923188840741</v>
+        <v>2.865539017136698</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.111325671891534</v>
+        <v>-3.237428418657508</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.524345195337049</v>
+        <v>1.570211225359948</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6761232592555214</v>
+        <v>0.5500205124895476</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.174905843960723</v>
+        <v>3.195551324630427</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.773392828038488</v>
+        <v>2.869699956767776</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.130824128133542</v>
+        <v>-3.256926874899516</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.520706752471324</v>
+        <v>1.566572782494223</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6280386179756171</v>
+        <v>0.5019358712096433</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.150215998823859</v>
+        <v>3.170861479493563</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.779272430566325</v>
+        <v>2.875579559295613</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.086621291047642</v>
+        <v>-3.212724037813616</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.544267489833521</v>
+        <v>1.59013351985642</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6722414550615176</v>
+        <v>0.5461387082955438</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.182617303603236</v>
+        <v>3.20326278427294</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.777682431035573</v>
+        <v>2.873989559764861</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.123600318711085</v>
+        <v>-3.249703065477059</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.527885879237392</v>
+        <v>1.57375190926029</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7092153568528481</v>
+        <v>0.5831126100868743</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.203211645147282</v>
+        <v>3.223857125816986</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.828930196218613</v>
+        <v>2.925237324947901</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.965308901171813</v>
+        <v>-3.091411647937787</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.64245021143614</v>
+        <v>1.688316241459039</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7092153568528481</v>
+        <v>0.5831126100868743</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.254459410330322</v>
+        <v>3.275104891000026</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.827370900812866</v>
+        <v>2.923678029542154</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.757666897537337</v>
+        <v>-2.883769644303311</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.723947717484184</v>
+        <v>1.769813747507082</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9168573604873242</v>
+        <v>0.7907546137213505</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.37748531710526</v>
+        <v>3.398130797774964</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.822319129051136</v>
+        <v>2.918626257780424</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.706634804814809</v>
+        <v>-2.832737551580783</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.739308782811465</v>
+        <v>1.785174812834364</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9678894532098522</v>
+        <v>0.8417867064438784</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.403052800977047</v>
+        <v>3.423698281646751</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.839506533143841</v>
+        <v>2.935813661873129</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.641410623687603</v>
+        <v>-2.767513370453577</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.782585859355052</v>
+        <v>1.828451889377951</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.033113634337058</v>
+        <v>0.9070108875710841</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.459374713746076</v>
+        <v>3.48002019441578</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.835467505443121</v>
+        <v>2.931774634172409</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.60398360361647</v>
+        <v>-2.730086350382444</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.793517639682786</v>
+        <v>1.839383669705684</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.038365172366239</v>
+        <v>0.9122624256002657</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.458486608862865</v>
+        <v>3.479132089532569</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.836724297774361</v>
+        <v>2.933031426503649</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.624095259651178</v>
+        <v>-2.750198006417152</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.786729769600143</v>
+        <v>1.832595799623042</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.049392517363658</v>
+        <v>0.9232897705976849</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.466359808192557</v>
+        <v>3.487005288862261</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.997282068795572</v>
+        <v>3.09358919752486</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.570350445223973</v>
+        <v>-2.696453191989947</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.968785466392236</v>
+        <v>2.014651496415134</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.059455826804121</v>
+        <v>0.9333530800381469</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.632955564878045</v>
+        <v>3.653601045547749</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.117394978013389</v>
+        <v>3.213702106742677</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.495568184198961</v>
+        <v>-2.621670930964934</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.118811280020058</v>
+        <v>2.164677310042956</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.134238087829133</v>
+        <v>1.00813534106316</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.79793783071087</v>
+        <v>3.818583311380574</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.109102954027248</v>
+        <v>3.205410082756536</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.469484099935153</v>
+        <v>-2.595586846701126</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.12095288973944</v>
+        <v>2.166818919762338</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.134238087829133</v>
+        <v>1.00813534106316</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.789645806724729</v>
+        <v>3.810291287394433</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.107296149611028</v>
+        <v>3.203603278340316</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.391352919086206</v>
+        <v>-2.51745566585218</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.150398557662798</v>
+        <v>2.196264587685697</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.208414898712818</v>
+        <v>1.082312151946844</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.832345088838719</v>
+        <v>3.852990569508423</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.124850555337819</v>
+        <v>3.221157684067107</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.382460457692923</v>
+        <v>-2.508563204458897</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.171509947946903</v>
+        <v>2.217375977969801</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.208414898712818</v>
+        <v>1.082312151946844</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.84989949456551</v>
+        <v>3.870544975235214</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.116705602742403</v>
+        <v>3.213012731471691</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.550936574662801</v>
+        <v>-2.677039321428774</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.095974548563536</v>
+        <v>2.141840578586434</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.180467062996237</v>
+        <v>1.054364316230264</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.824985840540146</v>
+        <v>3.84563132120985</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.097975299930265</v>
+        <v>3.194282428659553</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.853137045801217</v>
+        <v>-1.979239792567191</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.356364057296031</v>
+        <v>2.402230087318929</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.110119003625826</v>
+        <v>0.9840162568598529</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.764046702105761</v>
+        <v>3.784692182775465</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.08863932242717</v>
+        <v>3.184946451156458</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.830415942118065</v>
+        <v>-1.956518688884039</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.356116521266197</v>
+        <v>2.401982551289095</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.110119003625826</v>
+        <v>0.9840162568598529</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.754710724602666</v>
+        <v>3.77535620527237</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.247545448278339</v>
+        <v>3.343852577007627</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.959617755412107</v>
+        <v>-2.085720502178081</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.463341921799748</v>
+        <v>2.509207951822647</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9809171903317842</v>
+        <v>0.8548144435658107</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.836095762477409</v>
+        <v>3.856741243147114</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.284623270771985</v>
+        <v>3.380930399501273</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.114398762190362</v>
+        <v>-2.240501508956337</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.438507341582093</v>
+        <v>2.484373371604991</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.947549516277308</v>
+        <v>0.8214467695113346</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.85315298053837</v>
+        <v>3.873798461208074</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.28129862676153</v>
+        <v>3.377605755490818</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.107344071975189</v>
+        <v>-2.233446818741163</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.438004573657707</v>
+        <v>2.483870603680606</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9546042064924818</v>
+        <v>0.8285014597265083</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.854061150657019</v>
+        <v>3.874706631326724</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.291304780406272</v>
+        <v>3.38761190913556</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.080392847648701</v>
+        <v>-2.206495594414675</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.458791217033044</v>
+        <v>2.504657247055943</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8433818057542275</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.872995511918393</v>
+        <v>3.893640992588097</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.475407912551232</v>
+        <v>3.57171504128052</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.216345855705017</v>
+        <v>-2.342448602470991</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.588513145955478</v>
+        <v>2.634379175978376</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8433818057542275</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.057098644063353</v>
+        <v>4.077744124733057</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.467524607454225</v>
+        <v>3.563831736183513</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.238753973509889</v>
+        <v>-2.364856720275863</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.571666593736522</v>
+        <v>2.61753262375942</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8433818057542275</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.049215338966346</v>
+        <v>4.06986081963605</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.469578607003862</v>
+        <v>3.56588573573315</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.386759740989288</v>
+        <v>-2.512862487755263</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.5145182862944</v>
+        <v>2.560384316317298</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8827575436566595</v>
+        <v>0.756654796890686</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999233133197858</v>
+        <v>4.019878613867562</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.525832324725709</v>
+        <v>3.622139453454997</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.396200666877818</v>
+        <v>-2.522303413643793</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.566995633660835</v>
+        <v>2.612861663683733</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.005184661200051</v>
+        <v>0.8790819144340775</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.12894312144574</v>
+        <v>4.149588602115444</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.52872341927101</v>
+        <v>3.625030548000298</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.44847427421346</v>
+        <v>-2.574577020979434</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.548977285271879</v>
+        <v>2.594843315294777</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8268083070984362</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100470051589657</v>
+        <v>4.12111553225936</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.526835232164785</v>
+        <v>3.623142360894073</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.524804251814365</v>
+        <v>-2.65090699858034</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.516557107125292</v>
+        <v>2.56242313714819</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8268083070984362</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098581864483432</v>
+        <v>4.119227345153135</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.521655461767648</v>
+        <v>3.617962590496936</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.636561204429666</v>
+        <v>-2.762663951195641</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.466674555682034</v>
+        <v>2.512540585704932</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8411541012491086</v>
+        <v>0.7150513544831352</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.026347922517113</v>
+        <v>4.046993403186817</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.5200894719778</v>
+        <v>3.616396600707088</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.634720185371415</v>
+        <v>-2.76082293213739</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.465844973515487</v>
+        <v>2.511711003538385</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7163195811546036</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.025542868730146</v>
+        <v>4.04618834939985</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.533162878843719</v>
+        <v>3.629470007573007</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.767021477468969</v>
+        <v>-2.893124224234943</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.425997863542384</v>
+        <v>2.471863893565282</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7163195811546036</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.038616275596065</v>
+        <v>4.059261756265769</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.533162878843719</v>
+        <v>3.629470007573007</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.768583120283829</v>
+        <v>-2.894685867049803</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.42537320641644</v>
+        <v>2.471239236439338</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7163195811546036</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.038616275596065</v>
+        <v>4.059261756265769</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.531686919970721</v>
+        <v>3.627994048700009</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.796483907393302</v>
+        <v>-2.922586654159276</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.412736932699652</v>
+        <v>2.458602962722551</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8078254037776422</v>
+        <v>0.6817226570116688</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.016382162237306</v>
+        <v>4.03702764290701</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.528451363947919</v>
+        <v>3.624758492677207</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.919010010096196</v>
+        <v>-3.04511275686217</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.360490935595694</v>
+        <v>2.406356965618592</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6852993010747483</v>
+        <v>0.5591965543087749</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.939630944592769</v>
+        <v>3.960276425262473</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.595157323538423</v>
+        <v>3.691464452267711</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.939071331372702</v>
+        <v>-3.065174078138677</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.419172366675595</v>
+        <v>2.465038396698493</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6652379797982413</v>
+        <v>0.5391352330322678</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.994300111417368</v>
+        <v>4.014945592087072</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199806</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.73546904254027</v>
+        <v>3.831776171269558</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.195792149367526</v>
+        <v>-3.321894896133501</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.456795758479513</v>
+        <v>2.502661788502411</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.069563085932926</v>
+        <v>4.09020856660263</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.80444931168591</v>
+        <v>3.900756440415198</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.349778567143667</v>
+        <v>-3.475881313909642</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.464181460514696</v>
+        <v>2.510047490537594</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.138543355078566</v>
+        <v>4.15918883574827</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.790500513806031</v>
+        <v>3.886807642535319</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.299256663316001</v>
+        <v>-3.425359410081976</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.470441424165883</v>
+        <v>2.516307454188781</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.124594557198687</v>
+        <v>4.14524003786839</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.802371002861445</v>
+        <v>3.898678131590733</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.551731817323725</v>
+        <v>-3.6778345640897</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.381321851618207</v>
+        <v>2.427187881641105</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.136465046254101</v>
+        <v>4.157110526923805</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.803581537380389</v>
+        <v>3.899888666109677</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.821204619245433</v>
+        <v>-3.947307366011408</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.274743265368468</v>
+        <v>2.320609295391366</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.430720658888453</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.137675580773045</v>
+        <v>4.158321061442749</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.80770327960771</v>
+        <v>3.904010408336998</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.978748690974875</v>
+        <v>-4.10485143774085</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.215847378904013</v>
+        <v>2.261713408926911</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.489921600514152</v>
+        <v>0.3638188537481785</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.101656239916202</v>
+        <v>4.122301720585905</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301344</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.802781132343899</v>
+        <v>3.899088261073187</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.256713086558149</v>
+        <v>-4.382815833324123</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.099739473406893</v>
+        <v>2.145605503429791</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2741991194626943</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.0429622520811</v>
+        <v>4.063607732750804</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.964985189042944</v>
+        <v>4.061292317772232</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.37368077919704</v>
+        <v>-4.499783525963014</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.215156453050381</v>
+        <v>2.261022483073279</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2741991194626943</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.205166308780145</v>
+        <v>4.225811789449848</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.959831827006758</v>
+        <v>4.056138955736046</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.496460381166054</v>
+        <v>-4.65490500354358</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.160891250226589</v>
+        <v>2.193820530004866</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3367851668275899</v>
+        <v>0.2060920905147869</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.161902927103312</v>
+        <v>4.179794210044918</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.970061244575249</v>
+        <v>4.066368373304537</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.578395199434937</v>
+        <v>-4.736839821812463</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.138346740487527</v>
+        <v>2.171276020265805</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3268504212405097</v>
+        <v>0.1961573449277067</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.166171497319556</v>
+        <v>4.184062780261161</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.978986883031151</v>
+        <v>4.075294011760439</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.524657026034675</v>
+        <v>-4.683101648412201</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.168767648303534</v>
+        <v>2.201696928081811</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3805885946407718</v>
+        <v>0.2498955183279688</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.207340039815614</v>
+        <v>4.225231322757221</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616949</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.971139770275327</v>
+        <v>4.067446899004615</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.414650742557454</v>
+        <v>-4.573095364934979</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.204923048938598</v>
+        <v>2.237852328716876</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.403793166558047</v>
+        <v>0.273100090245244</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.213415670210155</v>
+        <v>4.231306953151762</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203663</v>
+        <v>3.785578085203664</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.975389780997301</v>
+        <v>4.071696909726589</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.271591166816528</v>
+        <v>-4.430035789194054</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.266396889956943</v>
+        <v>2.29932616973522</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4118065931480263</v>
+        <v>0.2811135168352233</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.222473736886117</v>
+        <v>4.240365019827723</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436929</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.982650663879838</v>
+        <v>4.078957792609126</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.97014444134469</v>
+        <v>-4.128589063722217</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.394236463028214</v>
+        <v>2.427165742806492</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7132533186198635</v>
+        <v>0.5825602423070606</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.410602655051756</v>
+        <v>4.428493937993363</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.983621841632548</v>
+        <v>4.079928970361836</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.025099637787759</v>
+        <v>-4.183544260165286</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.373225562203697</v>
+        <v>2.406154841981974</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7132533186198635</v>
+        <v>0.5825602423070606</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.411573832804466</v>
+        <v>4.429465115746073</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.984464746012303</v>
+        <v>4.080771874741592</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.974061261781239</v>
+        <v>-4.132505884158766</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.39448381698606</v>
+        <v>2.427413096764338</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7132533186198635</v>
+        <v>0.5825602423070606</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.412416737184222</v>
+        <v>4.430308020125828</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.003502844886449</v>
+        <v>4.099809973615737</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.932921966914608</v>
+        <v>-4.091366589292135</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.429977633806859</v>
+        <v>2.462906913585136</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7543926134864943</v>
+        <v>0.6236995371736914</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.456138412978346</v>
+        <v>4.474029695919952</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.82576709308562</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.819686841010383</v>
+        <v>3.915993969739672</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.822315826835006</v>
+        <v>-3.980760449212533</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.290404085962634</v>
+        <v>2.323333365740911</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8649987535660963</v>
+        <v>0.7343056772532934</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.338686093150042</v>
+        <v>4.356577376091648</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,45 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.84171412926164</v>
+        <v>3.804703121462781</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.823188885084347</v>
+        <v>3.919496013813635</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.952896561365849</v>
+        <v>-4.111341183743376</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.24167383622426</v>
+        <v>2.274603116002538</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7344180190352538</v>
+        <v>0.6037249427224509</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.263839696505499</v>
+        <v>4.281730979447106</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="2" t="n">
+        <v>45497</v>
+      </c>
+      <c r="B2035" t="n">
+        <v>3.842510502870751</v>
+      </c>
+      <c r="C2035" t="n">
+        <v>3.916127795630812</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>-4.111341183743376</v>
+      </c>
+      <c r="E2035" t="n">
+        <v>2.274603116002538</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>0.6037249427224509</v>
+      </c>
+      <c r="G2035" t="n">
+        <v>3.90919159261718</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.3%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-572.7%</t>
+          <t>-556.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.8%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-119.5%</t>
+          <t>-128.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-163.6%</t>
+          <t>-150.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>-64.7%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.15138198889114</v>
+        <v>-7.025279242125166</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2978420042916605</v>
+        <v>0.34828310299805</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.003265731997947</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.556791784963096</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.001715597883625</v>
+        <v>-6.875612851117651</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3548163503817072</v>
+        <v>0.4052574490880967</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9103622407554106</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.609641669395659</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.869440124252739</v>
+        <v>-6.743337377486765</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4030940265810887</v>
+        <v>0.4535351252874782</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.778086767124524</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.684374440321218</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.713701791692997</v>
+        <v>-6.587599044927023</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4682044202926221</v>
+        <v>0.518645518999012</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6223484345647824</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.780632500544699</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.464701993009416</v>
+        <v>-6.338599246243442</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5807106809897133</v>
+        <v>0.6311517796961028</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6223484345647824</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.793538841768358</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.57029198278252</v>
+        <v>-6.444189236016546</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4104987554812531</v>
+        <v>0.4609398541876426</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7279384243378867</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.602208918305277</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.589026884901117</v>
+        <v>-6.462924138135143</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4515491365109003</v>
+        <v>0.5019902352172902</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.733534433998018</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.647395654386284</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.441086843493518</v>
+        <v>-6.314984096727544</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3908462303857725</v>
+        <v>0.4412873290921624</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7132135180894604</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.539709281243251</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.388117321239529</v>
+        <v>-6.262014574473556</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4033200530338901</v>
+        <v>0.4537611517402795</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.562777008342167</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.344568914468839</v>
+        <v>-6.218466167702865</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4137788036470731</v>
+        <v>0.4642199023534626</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.555816396247073</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.31120570799007</v>
+        <v>-6.185102961224096</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4415864406197234</v>
+        <v>0.4920275393261129</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.570278750628217</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.202946570867549</v>
+        <v>-6.076843824101575</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4794222159279271</v>
+        <v>0.5298633146343166</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6602439958354716</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.564810871087412</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.079655436050418</v>
+        <v>-5.953552689284444</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5262367638653562</v>
+        <v>0.5766778625717461</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5369528610183411</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.636283645988267</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.058506237146974</v>
+        <v>-5.932403490381001</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.542397421664059</v>
+        <v>0.5928385203704485</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5158036621148977</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.656674143567658</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.81474079516353</v>
+        <v>-5.688638048397556</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6356843068044875</v>
+        <v>0.686125405510877</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5158036621148977</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.652454851914709</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.712977974886235</v>
+        <v>-5.586875228120261</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6785137488354214</v>
+        <v>0.7289548475418108</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.502584593722469</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.662510606870182</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.463127580937161</v>
+        <v>-5.337024834171187</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7711959813987534</v>
+        <v>0.8216370801051429</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.502584593722469</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.655252681853884</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.287235488469728</v>
+        <v>-5.161132741703755</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8451519419063751</v>
+        <v>0.8955930406127646</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.502584593722469</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.658851805374533</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.115789025447264</v>
+        <v>-4.989686278681291</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9270580331699145</v>
+        <v>0.9774991318763036</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3311381307000059</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.775047189242564</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.041499459708925</v>
+        <v>-4.915396712942952</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9557943370815472</v>
+        <v>1.006235435787936</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2568485649616666</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.818641406301865</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.977863717474991</v>
+        <v>-4.851760970709018</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.985943435029438</v>
+        <v>1.036384533735827</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.193212822727732</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.861517652696543</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.866436958149071</v>
+        <v>-4.740334211383098</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.011708397543602</v>
+        <v>1.062149496249991</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.193212822727732</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.842711911480338</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.62600646134421</v>
+        <v>-4.499903714578237</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.109623672890423</v>
+        <v>1.160064771596812</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.04721767407712824</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.988713286188132</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.553763893173016</v>
+        <v>-4.427661146407043</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.142450013993721</v>
+        <v>1.192891112700111</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.04721767407712824</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.992642600022952</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.53605020629515</v>
+        <v>-4.409947459529177</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.150214072662207</v>
+        <v>1.200655171368597</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.05039900297404504</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.995229981278442</v>
+        <v>3.070891629338026</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.427245320815423</v>
+        <v>-4.30114257404945</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.190734098074092</v>
+        <v>1.241175196780481</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.05039900297404504</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.992228052498436</v>
+        <v>3.06788970055802</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.207224522778413</v>
+        <v>-4.08112177601244</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.28032145429951</v>
+        <v>1.330762553005899</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1916188480420253</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.078538996549838</v>
+        <v>3.154200644609422</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.074356833715135</v>
+        <v>-3.948254086949162</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.349362712726645</v>
+        <v>1.399803811433034</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1916188480420253</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.094433179351661</v>
+        <v>3.170094827411245</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.954183750350636</v>
+        <v>-3.828081003584662</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.398577790512746</v>
+        <v>1.449018889219135</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3117919314065242</v>
+        <v>0.437894678172498</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.167682873810663</v>
+        <v>3.243344521870247</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.809511605250899</v>
+        <v>-3.683408858484925</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.466534751114081</v>
+        <v>1.51697584982047</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4564640765062616</v>
+        <v>0.5825668232722354</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.264574263431945</v>
+        <v>3.340235911491529</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.869386432608591</v>
+        <v>-3.743283685842617</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.428622311572429</v>
+        <v>1.479063410278819</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3965892491485695</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.214686858418755</v>
+        <v>3.29034850647834</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.749566201697754</v>
+        <v>-3.62346345493178</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.491839573170973</v>
+        <v>1.542280671877363</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3965892491485695</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.229976027652964</v>
+        <v>3.305637675712548</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.75203590815956</v>
+        <v>-3.625933161393586</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.398495889908692</v>
+        <v>1.448936988615082</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3941195426867634</v>
+        <v>0.5202222894527371</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.136138403098322</v>
+        <v>3.211800051157906</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.82040609448357</v>
+        <v>-3.694303347717596</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.29040967686439</v>
+        <v>1.340850775570779</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.060965684005352</v>
+        <v>3.136627332064936</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.834194147330616</v>
+        <v>-3.708091400564642</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.275331164357462</v>
+        <v>1.325772263063852</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.051402392637244</v>
+        <v>3.127064040696828</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.889714223223206</v>
+        <v>-3.763611476457232</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.390153970692629</v>
+        <v>1.440595069399018</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.188433229329446</v>
+        <v>3.26409487738903</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.714239963430737</v>
+        <v>-3.588137216664763</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.464910906601404</v>
+        <v>1.515352005307794</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.193000461321234</v>
+        <v>3.268662109380818</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.825176216071985</v>
+        <v>-3.699073469306011</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.396278434306112</v>
+        <v>1.446719533012502</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4033952417229783</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.168742490082441</v>
+        <v>3.244404138142025</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.791512670599703</v>
+        <v>-3.665409923833729</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.338282165896475</v>
+        <v>1.388723264602864</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4370587871952601</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.117478930767259</v>
+        <v>3.193140578826844</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.73166005139598</v>
+        <v>-3.605557304630006</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.372395600010096</v>
+        <v>1.422836698716486</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4370587871952601</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.127651317199392</v>
+        <v>3.203312965258976</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.645416588369603</v>
+        <v>-3.519313841603629</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.401839255794507</v>
+        <v>1.452280354500897</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4370587871952601</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.122597587773252</v>
+        <v>3.198259235832837</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.690723407768583</v>
+        <v>-3.564620661002609</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.375492303479441</v>
+        <v>1.425933402185831</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3962486241860294</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.089887265412239</v>
+        <v>3.165548913471823</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.719756512470884</v>
+        <v>-3.59365376570491</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.364430934631622</v>
+        <v>1.414872033338011</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3962486241860294</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.090439138445341</v>
+        <v>3.166100786504925</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.626946031020025</v>
+        <v>-3.500843284254051</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.330827819103331</v>
+        <v>1.381268917809721</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4890591056368887</v>
+        <v>0.6151618524028625</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.075398119207222</v>
+        <v>3.151059767266806</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.671335500349453</v>
+        <v>-3.545232753583479</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.314945507296161</v>
+        <v>1.365386606002551</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.444669636307461</v>
+        <v>0.5707723830734348</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.050637913534166</v>
+        <v>3.126299561593751</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.558664282113202</v>
+        <v>-3.432561535347229</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.355089703102384</v>
+        <v>1.405530801808774</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5573408545437112</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.113316352987639</v>
+        <v>3.188978001047224</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.44628728093053</v>
+        <v>-3.320184534164556</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.40553179940612</v>
+        <v>1.45597289811251</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5573408545437112</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.118807648818307</v>
+        <v>3.194469296877891</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.474067678831883</v>
+        <v>-3.347964932065909</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.405916842014118</v>
+        <v>1.456357940720508</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5295604566423581</v>
+        <v>0.6556632034083318</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.113636611846034</v>
+        <v>3.189298259905618</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.592448351562021</v>
+        <v>-3.466345604796047</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.196920292922716</v>
+        <v>1.247361391629106</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4623426044913819</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.911661620556101</v>
+        <v>2.987323268615686</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.701062430005353</v>
+        <v>-3.574959683239379</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.273624322264589</v>
+        <v>1.324065420970979</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4623426044913819</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.031811281275307</v>
+        <v>3.107472929334891</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.66565339175721</v>
+        <v>-3.539550644991236</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.302300963666169</v>
+        <v>1.352742062372559</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4623426044913819</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.04632430737763</v>
+        <v>3.121985955437214</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.627269729199059</v>
+        <v>-3.501166982433085</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.315073870031799</v>
+        <v>1.365514968738188</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.500726267049533</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.06677394625489</v>
+        <v>3.142435594314474</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.450153399163892</v>
+        <v>-3.324050652397919</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.382649430891167</v>
+        <v>1.433090529597556</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.500726267049533</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.063502975100191</v>
+        <v>3.139164623159775</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.495245643997438</v>
+        <v>-3.369142897231464</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.365295924719662</v>
+        <v>1.415737023426051</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4388302238801433</v>
+        <v>0.564932970646117</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.02704874096047</v>
+        <v>3.102710389020055</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.31587022275867</v>
+        <v>-3.189767475992697</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.430833068521583</v>
+        <v>1.481274167227973</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5956069820508619</v>
+        <v>0.7217097288168357</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.114901771169316</v>
+        <v>3.190563419228901</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.360884436279277</v>
+        <v>-3.234781689513303</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.39363483844493</v>
+        <v>1.44407593715132</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5652580867362573</v>
+        <v>0.6913608335022311</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.077499889312143</v>
+        <v>3.153161537371727</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.627888946551712</v>
+        <v>-3.501786199785738</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.292524596674902</v>
+        <v>1.342965695381292</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3708950486933087</v>
+        <v>0.4969977954592826</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.96657362882532</v>
+        <v>3.042235276884904</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.729086727988885</v>
+        <v>-3.602983981222911</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.251249405996534</v>
+        <v>1.301690504702924</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3024862351479896</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.92473226259463</v>
+        <v>3.000393910654214</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.722575761374572</v>
+        <v>-3.596473014608598</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.251453754196576</v>
+        <v>1.301894852902966</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3024862351479896</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.922332224148946</v>
+        <v>2.99799387220853</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.703537633667275</v>
+        <v>-3.577434886901301</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.25559372448774</v>
+        <v>1.306034823194129</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.244302623816795</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.883946776558474</v>
+        <v>2.959608424618059</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.734664264817893</v>
+        <v>-3.608561518051919</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.420724940966173</v>
+        <v>1.471166039672563</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.244302623816795</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.061528645497155</v>
+        <v>3.137190293556739</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.74853102615181</v>
+        <v>-3.622428279385836</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.41601156541874</v>
+        <v>1.466452664125129</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2064447070829721</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.039647224442995</v>
+        <v>3.115308872502579</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.70372685461188</v>
+        <v>-3.577624107845907</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.439941764431638</v>
+        <v>1.490382863138027</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2064447070829721</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.045655754839921</v>
+        <v>3.121317402899505</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.555983884376878</v>
+        <v>-3.429881137610904</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.396989173802838</v>
+        <v>1.447430272509228</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3742520643178552</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.04429039045805</v>
+        <v>3.119952038517634</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.657998566908099</v>
+        <v>-3.531895820142125</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.358976922321831</v>
+        <v>1.40941802102822</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3742520643178552</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.047084011989531</v>
+        <v>3.122745660049115</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.651845860855315</v>
+        <v>-3.525743114089341</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.362100353134603</v>
+        <v>1.412541451840992</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3804047703706395</v>
+        <v>0.5065075171366133</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.05143798401286</v>
+        <v>3.127099632072444</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.918582727259874</v>
+        <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.668655159005816</v>
+        <v>-3.542552412239842</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.4507642393438</v>
+        <v>1.404898209320902</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3635954722201379</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.136740010591957</v>
+        <v>3.116094529922254</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.984918281056695</v>
+        <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.606357160229694</v>
+        <v>-3.480254413463721</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.54201899265107</v>
+        <v>1.496152962628172</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3635954722201379</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.203075564388778</v>
+        <v>3.182430083719074</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.787210282770822</v>
+        <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.404566962564537</v>
+        <v>-3.278464215798563</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.42502707343126</v>
+        <v>1.379161043408362</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5616136643892923</v>
+        <v>0.687716411155266</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.124178481404398</v>
+        <v>3.103533000734694</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.857500515092998</v>
+        <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.455453675250731</v>
+        <v>-3.329350928484757</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.474962620678958</v>
+        <v>1.429096590656059</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5107269517030978</v>
+        <v>0.6368296984690716</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.163936686114857</v>
+        <v>3.143291205445153</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.872128251209041</v>
+        <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.553194219875706</v>
+        <v>-3.427091473109732</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.450494138945012</v>
+        <v>1.404628108922113</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4948376735701175</v>
+        <v>0.6209404203360913</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.169030855351112</v>
+        <v>3.148385374681408</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.870664232033713</v>
+        <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.61340351788099</v>
+        <v>-3.487300771115016</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.42494640056757</v>
+        <v>1.379080370544671</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.434628375564833</v>
+        <v>0.5607311223308068</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.131441257372613</v>
+        <v>3.110795776702909</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.869155850073641</v>
+        <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.536981471449063</v>
+        <v>-3.410878724683089</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.454006837180269</v>
+        <v>1.40814080715737</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.434628375564833</v>
+        <v>0.5607311223308068</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.129932875412542</v>
+        <v>3.109287394742838</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.869018717509078</v>
+        <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.492608339810495</v>
+        <v>-3.366505593044521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.471618957271132</v>
+        <v>1.425752927248234</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4790015072034016</v>
+        <v>0.6051042539693754</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.156419621831119</v>
+        <v>3.135774141161415</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.863412511647668</v>
+        <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.369774118923327</v>
+        <v>-3.243671372157353</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.51514643976459</v>
+        <v>1.469280409741691</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4790015072034016</v>
+        <v>0.6051042539693754</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.150813415969709</v>
+        <v>3.130167935300006</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.869794268675473</v>
+        <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.322118388362272</v>
+        <v>-3.196015641596298</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.540590489016817</v>
+        <v>1.494724458993918</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5266572377644573</v>
+        <v>0.652759984530431</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.185788611334147</v>
+        <v>3.165143130664444</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.874686642050198</v>
+        <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.221600229863517</v>
+        <v>-3.095497483097543</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.585690125791043</v>
+        <v>1.539824095768145</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6271753962632118</v>
+        <v>0.7532781430291856</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.250991879808125</v>
+        <v>3.230346399138421</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.86144131452607</v>
+        <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.282266820265906</v>
+        <v>-3.156164073499932</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.54817816210596</v>
+        <v>1.502312132083061</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5454770795446782</v>
+        <v>0.6715798263106519</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.188727562252877</v>
+        <v>3.168082081583173</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.865539017136698</v>
+        <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.237428418657508</v>
+        <v>-3.111325671891534</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.570211225359948</v>
+        <v>1.524345195337049</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5500205124895476</v>
+        <v>0.6761232592555214</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.195551324630427</v>
+        <v>3.174905843960723</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.869699956767776</v>
+        <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.256926874899516</v>
+        <v>-3.130824128133542</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.566572782494223</v>
+        <v>1.520706752471324</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5019358712096433</v>
+        <v>0.6280386179756171</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.170861479493563</v>
+        <v>3.150215998823859</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.875579559295613</v>
+        <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.212724037813616</v>
+        <v>-3.086621291047642</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.59013351985642</v>
+        <v>1.544267489833521</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5461387082955438</v>
+        <v>0.6722414550615176</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.20326278427294</v>
+        <v>3.182617303603236</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.873989559764861</v>
+        <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.249703065477059</v>
+        <v>-3.123600318711085</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.57375190926029</v>
+        <v>1.527885879237392</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5831126100868743</v>
+        <v>0.7092153568528481</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.223857125816986</v>
+        <v>3.203211645147282</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.925237324947901</v>
+        <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.091411647937787</v>
+        <v>-2.965308901171813</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.688316241459039</v>
+        <v>1.64245021143614</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5831126100868743</v>
+        <v>0.7092153568528481</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.275104891000026</v>
+        <v>3.254459410330322</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.923678029542154</v>
+        <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.883769644303311</v>
+        <v>-2.757666897537337</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.769813747507082</v>
+        <v>1.723947717484184</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7907546137213505</v>
+        <v>0.9168573604873242</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.398130797774964</v>
+        <v>3.37748531710526</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.918626257780424</v>
+        <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.832737551580783</v>
+        <v>-2.706634804814809</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.785174812834364</v>
+        <v>1.739308782811465</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8417867064438784</v>
+        <v>0.9678894532098522</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.423698281646751</v>
+        <v>3.403052800977047</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.935813661873129</v>
+        <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.767513370453577</v>
+        <v>-2.641410623687603</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.828451889377951</v>
+        <v>1.782585859355052</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9070108875710841</v>
+        <v>1.033113634337058</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.48002019441578</v>
+        <v>3.459374713746076</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.931774634172409</v>
+        <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.730086350382444</v>
+        <v>-2.60398360361647</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.839383669705684</v>
+        <v>1.793517639682786</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9122624256002657</v>
+        <v>1.038365172366239</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.479132089532569</v>
+        <v>3.458486608862865</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.933031426503649</v>
+        <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.750198006417152</v>
+        <v>-2.624095259651178</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.832595799623042</v>
+        <v>1.786729769600143</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9232897705976849</v>
+        <v>1.049392517363658</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.487005288862261</v>
+        <v>3.466359808192557</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.09358919752486</v>
+        <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.696453191989947</v>
+        <v>-2.570350445223973</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.014651496415134</v>
+        <v>1.968785466392236</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9333530800381469</v>
+        <v>1.059455826804121</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.653601045547749</v>
+        <v>3.632955564878045</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.213702106742677</v>
+        <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.621670930964934</v>
+        <v>-2.495568184198961</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.164677310042956</v>
+        <v>2.118811280020058</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.00813534106316</v>
+        <v>1.134238087829133</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.818583311380574</v>
+        <v>3.79793783071087</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.205410082756536</v>
+        <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.595586846701126</v>
+        <v>-2.469484099935153</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.166818919762338</v>
+        <v>2.12095288973944</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.00813534106316</v>
+        <v>1.134238087829133</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.810291287394433</v>
+        <v>3.789645806724729</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.203603278340316</v>
+        <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.51745566585218</v>
+        <v>-2.391352919086206</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.196264587685697</v>
+        <v>2.150398557662798</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.082312151946844</v>
+        <v>1.208414898712818</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.852990569508423</v>
+        <v>3.832345088838719</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.221157684067107</v>
+        <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.508563204458897</v>
+        <v>-2.382460457692923</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.217375977969801</v>
+        <v>2.171509947946903</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.082312151946844</v>
+        <v>1.208414898712818</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.870544975235214</v>
+        <v>3.84989949456551</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.213012731471691</v>
+        <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.677039321428774</v>
+        <v>-2.550936574662801</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.141840578586434</v>
+        <v>2.095974548563536</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.054364316230264</v>
+        <v>1.180467062996237</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.84563132120985</v>
+        <v>3.824985840540146</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.194282428659553</v>
+        <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.979239792567191</v>
+        <v>-1.853137045801217</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.402230087318929</v>
+        <v>2.356364057296031</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9840162568598529</v>
+        <v>1.110119003625826</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.784692182775465</v>
+        <v>3.764046702105761</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.184946451156458</v>
+        <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.956518688884039</v>
+        <v>-1.830415942118065</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.401982551289095</v>
+        <v>2.356116521266197</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9840162568598529</v>
+        <v>1.110119003625826</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.77535620527237</v>
+        <v>3.754710724602666</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.343852577007627</v>
+        <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.085720502178081</v>
+        <v>-1.959617755412107</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.509207951822647</v>
+        <v>2.463341921799748</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8548144435658107</v>
+        <v>0.9809171903317842</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.856741243147114</v>
+        <v>3.836095762477409</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.380930399501273</v>
+        <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.240501508956337</v>
+        <v>-2.114398762190362</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.484373371604991</v>
+        <v>2.438507341582093</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8214467695113346</v>
+        <v>0.947549516277308</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.873798461208074</v>
+        <v>3.85315298053837</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.377605755490818</v>
+        <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.233446818741163</v>
+        <v>-2.107344071975189</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.483870603680606</v>
+        <v>2.438004573657707</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8285014597265083</v>
+        <v>0.9546042064924818</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.874706631326724</v>
+        <v>3.854061150657019</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.38761190913556</v>
+        <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.206495594414675</v>
+        <v>-2.080392847648701</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.504657247055943</v>
+        <v>2.458791217033044</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8433818057542275</v>
+        <v>0.9694845525202009</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.893640992588097</v>
+        <v>3.872995511918393</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.57171504128052</v>
+        <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.342448602470991</v>
+        <v>-2.216345855705017</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.634379175978376</v>
+        <v>2.588513145955478</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8433818057542275</v>
+        <v>0.9694845525202009</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.077744124733057</v>
+        <v>4.057098644063353</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.563831736183513</v>
+        <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.364856720275863</v>
+        <v>-2.238753973509889</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.61753262375942</v>
+        <v>2.571666593736522</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8433818057542275</v>
+        <v>0.9694845525202009</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.06986081963605</v>
+        <v>4.049215338966346</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.56588573573315</v>
+        <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.512862487755263</v>
+        <v>-2.386759740989288</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.560384316317298</v>
+        <v>2.5145182862944</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.756654796890686</v>
+        <v>0.8827575436566595</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.019878613867562</v>
+        <v>3.999233133197858</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.622139453454997</v>
+        <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.522303413643793</v>
+        <v>-2.396200666877818</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.612861663683733</v>
+        <v>2.566995633660835</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8790819144340775</v>
+        <v>1.005184661200051</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.149588602115444</v>
+        <v>4.12894312144574</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.625030548000298</v>
+        <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.574577020979434</v>
+        <v>-2.44847427421346</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.594843315294777</v>
+        <v>2.548977285271879</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8268083070984362</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.12111553225936</v>
+        <v>4.100470051589657</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.623142360894073</v>
+        <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.65090699858034</v>
+        <v>-2.524804251814365</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.56242313714819</v>
+        <v>2.516557107125292</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8268083070984362</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.119227345153135</v>
+        <v>4.098581864483432</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.617962590496936</v>
+        <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.762663951195641</v>
+        <v>-2.636561204429666</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.512540585704932</v>
+        <v>2.466674555682034</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7150513544831352</v>
+        <v>0.8411541012491086</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.046993403186817</v>
+        <v>4.026347922517113</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.616396600707088</v>
+        <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.76082293213739</v>
+        <v>-2.634720185371415</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.511711003538385</v>
+        <v>2.465844973515487</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7163195811546036</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.04618834939985</v>
+        <v>4.025542868730146</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647106</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.629470007573007</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.893124224234943</v>
+        <v>-2.767021477468969</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.471863893565282</v>
+        <v>2.425997863542384</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7163195811546036</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.059261756265769</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.629470007573007</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.894685867049803</v>
+        <v>-2.768583120283829</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.471239236439338</v>
+        <v>2.42537320641644</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7163195811546036</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.059261756265769</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392116</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.627994048700009</v>
+        <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.922586654159276</v>
+        <v>-2.796483907393302</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.458602962722551</v>
+        <v>2.412736932699652</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6817226570116688</v>
+        <v>0.8078254037776422</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.03702764290701</v>
+        <v>4.016382162237306</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172527</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.624758492677207</v>
+        <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.04511275686217</v>
+        <v>-2.919010010096196</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.406356965618592</v>
+        <v>2.360490935595694</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5591965543087749</v>
+        <v>0.6852993010747483</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.960276425262473</v>
+        <v>3.939630944592769</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971078</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.691464452267711</v>
+        <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.065174078138677</v>
+        <v>-2.939071331372702</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.465038396698493</v>
+        <v>2.419172366675595</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5391352330322678</v>
+        <v>0.6652379797982413</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.014945592087072</v>
+        <v>3.994300111417368</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199806</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.831776171269558</v>
+        <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.321894896133501</v>
+        <v>-3.195792149367526</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.502661788502411</v>
+        <v>2.456795758479513</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.09020856660263</v>
+        <v>4.069563085932926</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622236</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.900756440415198</v>
+        <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.475881313909642</v>
+        <v>-3.349778567143667</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.510047490537594</v>
+        <v>2.464181460514696</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.15918883574827</v>
+        <v>4.138543355078566</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808528</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.886807642535319</v>
+        <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.425359410081976</v>
+        <v>-3.299256663316001</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.516307454188781</v>
+        <v>2.470441424165883</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.14524003786839</v>
+        <v>4.124594557198687</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994893</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.898678131590733</v>
+        <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.6778345640897</v>
+        <v>-3.551731817323725</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.427187881641105</v>
+        <v>2.381321851618207</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.157110526923805</v>
+        <v>4.136465046254101</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358298</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.899888666109677</v>
+        <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.947307366011408</v>
+        <v>-3.821204619245433</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.320609295391366</v>
+        <v>2.274743265368468</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.430720658888453</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.158321061442749</v>
+        <v>4.137675580773045</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.904010408336998</v>
+        <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.10485143774085</v>
+        <v>-3.978748690974875</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.261713408926911</v>
+        <v>2.215847378904013</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3638188537481785</v>
+        <v>0.489921600514152</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.122301720585905</v>
+        <v>4.101656239916202</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301344</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.899088261073187</v>
+        <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.382815833324123</v>
+        <v>-4.256713086558149</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.145605503429791</v>
+        <v>2.099739473406893</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2741991194626943</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.063607732750804</v>
+        <v>4.0429622520811</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
-        <v>4.061292317772232</v>
+        <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.499783525963014</v>
+        <v>-4.37368077919704</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.261022483073279</v>
+        <v>2.215156453050381</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2741991194626943</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.225811789449848</v>
+        <v>4.205166308780145</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
-        <v>4.056138955736046</v>
+        <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.65490500354358</v>
+        <v>-4.496460381166054</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.193820530004866</v>
+        <v>2.160891250226589</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2060920905147869</v>
+        <v>0.3367851668275899</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.179794210044918</v>
+        <v>4.161902927103312</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
-        <v>4.066368373304537</v>
+        <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.736839821812463</v>
+        <v>-4.578395199434937</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.171276020265805</v>
+        <v>2.138346740487527</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1961573449277067</v>
+        <v>0.3268504212405097</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.184062780261161</v>
+        <v>4.166171497319556</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
-        <v>4.075294011760439</v>
+        <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.683101648412201</v>
+        <v>-4.524657026034675</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.201696928081811</v>
+        <v>2.168767648303534</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2498955183279688</v>
+        <v>0.3805885946407718</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.225231322757221</v>
+        <v>4.207340039815614</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616949</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
-        <v>4.067446899004615</v>
+        <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.573095364934979</v>
+        <v>-4.414650742557454</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.237852328716876</v>
+        <v>2.204923048938598</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.273100090245244</v>
+        <v>0.403793166558047</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.231306953151762</v>
+        <v>4.213415670210155</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203664</v>
+        <v>3.785578085203663</v>
       </c>
       <c r="C2028" t="n">
-        <v>4.071696909726589</v>
+        <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.430035789194054</v>
+        <v>-4.271591166816528</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.29932616973522</v>
+        <v>2.266396889956943</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2811135168352233</v>
+        <v>0.4118065931480263</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.240365019827723</v>
+        <v>4.222473736886117</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436929</v>
       </c>
       <c r="C2029" t="n">
-        <v>4.078957792609126</v>
+        <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.128589063722217</v>
+        <v>-3.97014444134469</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.427165742806492</v>
+        <v>2.394236463028214</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5825602423070606</v>
+        <v>0.7132533186198635</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.428493937993363</v>
+        <v>4.410602655051756</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
-        <v>4.079928970361836</v>
+        <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.183544260165286</v>
+        <v>-4.025099637787759</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.406154841981974</v>
+        <v>2.373225562203697</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5825602423070606</v>
+        <v>0.7132533186198635</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.429465115746073</v>
+        <v>4.411573832804466</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
-        <v>4.080771874741592</v>
+        <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.132505884158766</v>
+        <v>-3.974061261781239</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.427413096764338</v>
+        <v>2.39448381698606</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5825602423070606</v>
+        <v>0.7132533186198635</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.430308020125828</v>
+        <v>4.412416737184222</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.099809973615737</v>
+        <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.091366589292135</v>
+        <v>-3.932921966914608</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.462906913585136</v>
+        <v>2.429977633806859</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6236995371736914</v>
+        <v>0.7543926134864943</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.474029695919952</v>
+        <v>4.456138412978346</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.82576709308562</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.915993969739672</v>
+        <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.980760449212533</v>
+        <v>-3.822315826835006</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.323333365740911</v>
+        <v>2.290404085962634</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7343056772532934</v>
+        <v>0.8649987535660963</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.356577376091648</v>
+        <v>4.338686093150042</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462781</v>
+        <v>3.804703121462782</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.919496013813635</v>
+        <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.111341183743376</v>
+        <v>-3.952896561365849</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.274603116002538</v>
+        <v>2.24167383622426</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6037249427224509</v>
+        <v>0.7344180190352538</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.281730979447106</v>
+        <v>4.263839696505499</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.842510502870751</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.916127795630812</v>
+        <v>3.819820666901524</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.111341183743376</v>
+        <v>-3.952896561365849</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.274603116002538</v>
+        <v>2.24167383622426</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6037249427224509</v>
+        <v>0.7344180190352538</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.90919159261718</v>
+        <v>3.812884463887892</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>455.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-556.9%</t>
+          <t>-569.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-157.1%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-128.3%</t>
+          <t>-128.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.7%</t>
+          <t>-69.5%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.410878724683089</v>
+        <v>-3.538080175137778</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.40814080715737</v>
+        <v>1.357260226975495</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5607311223308068</v>
@@ -46999,10 +46999,10 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.366505593044521</v>
+        <v>-3.49370704349921</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.425752927248234</v>
+        <v>1.374872347066358</v>
       </c>
       <c r="F1976" t="n">
         <v>0.6051042539693754</v>
@@ -47022,10 +47022,10 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.243671372157353</v>
+        <v>-3.370872822612042</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.469280409741691</v>
+        <v>1.418399829559816</v>
       </c>
       <c r="F1977" t="n">
         <v>0.6051042539693754</v>
@@ -47045,10 +47045,10 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.196015641596298</v>
+        <v>-3.323217092050987</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.494724458993918</v>
+        <v>1.443843878812043</v>
       </c>
       <c r="F1978" t="n">
         <v>0.652759984530431</v>
@@ -47068,10 +47068,10 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.095497483097543</v>
+        <v>-3.222698933552232</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.539824095768145</v>
+        <v>1.488943515586269</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7532781430291856</v>
@@ -47091,10 +47091,10 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.156164073499932</v>
+        <v>-3.283365523954621</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.502312132083061</v>
+        <v>1.451431551901186</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6715798263106519</v>
@@ -47114,10 +47114,10 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.111325671891534</v>
+        <v>-3.238527122346223</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.524345195337049</v>
+        <v>1.473464615155174</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6761232592555214</v>
@@ -47137,10 +47137,10 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.130824128133542</v>
+        <v>-3.258025578588231</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.520706752471324</v>
+        <v>1.469826172289448</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6280386179756171</v>
@@ -47160,10 +47160,10 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.086621291047642</v>
+        <v>-3.213822741502331</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.544267489833521</v>
+        <v>1.493386909651646</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6722414550615176</v>
@@ -47183,10 +47183,10 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.123600318711085</v>
+        <v>-3.250801769165774</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.527885879237392</v>
+        <v>1.477005299055516</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7092153568528481</v>
@@ -47206,10 +47206,10 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.965308901171813</v>
+        <v>-3.092510351626502</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.64245021143614</v>
+        <v>1.591569631254265</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7092153568528481</v>
@@ -47229,10 +47229,10 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.757666897537337</v>
+        <v>-2.884868347992026</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.723947717484184</v>
+        <v>1.673067137302308</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9168573604873242</v>
@@ -47252,10 +47252,10 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.706634804814809</v>
+        <v>-2.833836255269498</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.739308782811465</v>
+        <v>1.688428202629589</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9678894532098522</v>
@@ -47275,10 +47275,10 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.641410623687603</v>
+        <v>-2.768612074142292</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.782585859355052</v>
+        <v>1.731705279173177</v>
       </c>
       <c r="F1988" t="n">
         <v>1.033113634337058</v>
@@ -47298,10 +47298,10 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.60398360361647</v>
+        <v>-2.731185054071159</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.793517639682786</v>
+        <v>1.74263705950091</v>
       </c>
       <c r="F1989" t="n">
         <v>1.038365172366239</v>
@@ -47321,10 +47321,10 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.624095259651178</v>
+        <v>-2.751296710105867</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.786729769600143</v>
+        <v>1.735849189418267</v>
       </c>
       <c r="F1990" t="n">
         <v>1.049392517363658</v>
@@ -47344,10 +47344,10 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.570350445223973</v>
+        <v>-2.697551895678662</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.968785466392236</v>
+        <v>1.91790488621036</v>
       </c>
       <c r="F1991" t="n">
         <v>1.059455826804121</v>
@@ -47367,10 +47367,10 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.495568184198961</v>
+        <v>-2.62276963465365</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.118811280020058</v>
+        <v>2.067930699838183</v>
       </c>
       <c r="F1992" t="n">
         <v>1.134238087829133</v>
@@ -47390,10 +47390,10 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.469484099935153</v>
+        <v>-2.596685550389842</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.12095288973944</v>
+        <v>2.070072309557564</v>
       </c>
       <c r="F1993" t="n">
         <v>1.134238087829133</v>
@@ -47413,10 +47413,10 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.391352919086206</v>
+        <v>-2.518554369540895</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.150398557662798</v>
+        <v>2.099517977480923</v>
       </c>
       <c r="F1994" t="n">
         <v>1.208414898712818</v>
@@ -47436,10 +47436,10 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.382460457692923</v>
+        <v>-2.509661908147612</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.171509947946903</v>
+        <v>2.120629367765027</v>
       </c>
       <c r="F1995" t="n">
         <v>1.208414898712818</v>
@@ -47459,10 +47459,10 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.550936574662801</v>
+        <v>-2.67813802511749</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.095974548563536</v>
+        <v>2.04509396838166</v>
       </c>
       <c r="F1996" t="n">
         <v>1.180467062996237</v>
@@ -47482,10 +47482,10 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.853137045801217</v>
+        <v>-1.980338496255906</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.356364057296031</v>
+        <v>2.305483477114155</v>
       </c>
       <c r="F1997" t="n">
         <v>1.110119003625826</v>
@@ -47505,10 +47505,10 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.830415942118065</v>
+        <v>-1.957617392572754</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.356116521266197</v>
+        <v>2.305235941084321</v>
       </c>
       <c r="F1998" t="n">
         <v>1.110119003625826</v>
@@ -47528,10 +47528,10 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.959617755412107</v>
+        <v>-2.086819205866796</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.463341921799748</v>
+        <v>2.412461341617873</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9809171903317842</v>
@@ -47551,10 +47551,10 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.114398762190362</v>
+        <v>-2.241600212645052</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.438507341582093</v>
+        <v>2.387626761400217</v>
       </c>
       <c r="F2000" t="n">
         <v>0.947549516277308</v>
@@ -47574,10 +47574,10 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.107344071975189</v>
+        <v>-2.234545522429878</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.438004573657707</v>
+        <v>2.387123993475832</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9546042064924818</v>
@@ -47597,10 +47597,10 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.080392847648701</v>
+        <v>-2.20759429810339</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.458791217033044</v>
+        <v>2.407910636851168</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9694845525202009</v>
@@ -47620,10 +47620,10 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.216345855705017</v>
+        <v>-2.343547306159707</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.588513145955478</v>
+        <v>2.537632565773602</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9694845525202009</v>
@@ -47643,10 +47643,10 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.238753973509889</v>
+        <v>-2.365955423964579</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.571666593736522</v>
+        <v>2.520786013554646</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9694845525202009</v>
@@ -47666,10 +47666,10 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.386759740989288</v>
+        <v>-2.513961191443978</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.5145182862944</v>
+        <v>2.463637706112523</v>
       </c>
       <c r="F2005" t="n">
         <v>0.8827575436566595</v>
@@ -47689,10 +47689,10 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.396200666877818</v>
+        <v>-2.523402117332508</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.566995633660835</v>
+        <v>2.516115053478959</v>
       </c>
       <c r="F2006" t="n">
         <v>1.005184661200051</v>
@@ -47712,10 +47712,10 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.44847427421346</v>
+        <v>-2.575675724668149</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.548977285271879</v>
+        <v>2.498096705090003</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9529110538644098</v>
@@ -47735,10 +47735,10 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.524804251814365</v>
+        <v>-2.652005702269055</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.516557107125292</v>
+        <v>2.465676526943416</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9529110538644098</v>
@@ -47758,10 +47758,10 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.636561204429666</v>
+        <v>-2.763762654884356</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.466674555682034</v>
+        <v>2.415793975500158</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8411541012491086</v>
@@ -47781,10 +47781,10 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.634720185371415</v>
+        <v>-2.761921635826105</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.465844973515487</v>
+        <v>2.41496439333361</v>
       </c>
       <c r="F2010" t="n">
         <v>0.842422327920577</v>
@@ -47804,10 +47804,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.767021477468969</v>
+        <v>-2.894222927923658</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.425997863542384</v>
+        <v>2.375117283360508</v>
       </c>
       <c r="F2011" t="n">
         <v>0.842422327920577</v>
@@ -47827,10 +47827,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.768583120283829</v>
+        <v>-2.895784570738519</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.42537320641644</v>
+        <v>2.374492626234564</v>
       </c>
       <c r="F2012" t="n">
         <v>0.842422327920577</v>
@@ -47850,10 +47850,10 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.796483907393302</v>
+        <v>-2.923685357847992</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.412736932699652</v>
+        <v>2.361856352517777</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8078254037776422</v>
@@ -47873,10 +47873,10 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.919010010096196</v>
+        <v>-3.046211460550885</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.360490935595694</v>
+        <v>2.309610355413818</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6852993010747483</v>
@@ -47896,10 +47896,10 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.939071331372702</v>
+        <v>-3.066272781827392</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.419172366675595</v>
+        <v>2.368291786493719</v>
       </c>
       <c r="F2015" t="n">
         <v>0.6652379797982413</v>
@@ -47919,10 +47919,10 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.195792149367526</v>
+        <v>-3.322993599822216</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.456795758479513</v>
+        <v>2.405915178297636</v>
       </c>
       <c r="F2016" t="n">
         <v>0.5568234056544265</v>
@@ -47942,10 +47942,10 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.349778567143667</v>
+        <v>-3.476980017598357</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.464181460514696</v>
+        <v>2.41330088033282</v>
       </c>
       <c r="F2017" t="n">
         <v>0.5568234056544265</v>
@@ -47965,10 +47965,10 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.299256663316001</v>
+        <v>-3.426458113770691</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.470441424165883</v>
+        <v>2.419560843984007</v>
       </c>
       <c r="F2018" t="n">
         <v>0.5568234056544265</v>
@@ -47988,10 +47988,10 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.551731817323725</v>
+        <v>-3.678933267778415</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.381321851618207</v>
+        <v>2.330441271436332</v>
       </c>
       <c r="F2019" t="n">
         <v>0.5568234056544265</v>
@@ -48011,10 +48011,10 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.821204619245433</v>
+        <v>-3.948406069700123</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.274743265368468</v>
+        <v>2.223862685186592</v>
       </c>
       <c r="F2020" t="n">
         <v>0.5568234056544265</v>
@@ -48034,10 +48034,10 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.978748690974875</v>
+        <v>-4.105950141429565</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.215847378904013</v>
+        <v>2.164966798722137</v>
       </c>
       <c r="F2021" t="n">
         <v>0.489921600514152</v>
@@ -48057,10 +48057,10 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.256713086558149</v>
+        <v>-4.383914537012839</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.099739473406893</v>
+        <v>2.048858893225017</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4003018662286678</v>
@@ -48080,10 +48080,10 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.37368077919704</v>
+        <v>-4.500882229651729</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.215156453050381</v>
+        <v>2.164275872868505</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4003018662286678</v>
@@ -48103,10 +48103,10 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.496460381166054</v>
+        <v>-4.623661831620744</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.160891250226589</v>
+        <v>2.110010670044713</v>
       </c>
       <c r="F2024" t="n">
         <v>0.3367851668275899</v>
@@ -48126,10 +48126,10 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.578395199434937</v>
+        <v>-4.705596649889627</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.138346740487527</v>
+        <v>2.087466160305651</v>
       </c>
       <c r="F2025" t="n">
         <v>0.3268504212405097</v>
@@ -48149,10 +48149,10 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.524657026034675</v>
+        <v>-4.651858476489365</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.168767648303534</v>
+        <v>2.117887068121658</v>
       </c>
       <c r="F2026" t="n">
         <v>0.3805885946407718</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.414650742557454</v>
+        <v>-4.541852193012144</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.204923048938598</v>
+        <v>2.154042468756722</v>
       </c>
       <c r="F2027" t="n">
         <v>0.403793166558047</v>
@@ -48195,10 +48195,10 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.271591166816528</v>
+        <v>-4.398792617271218</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.266396889956943</v>
+        <v>2.215516309775067</v>
       </c>
       <c r="F2028" t="n">
         <v>0.4118065931480263</v>
@@ -48218,10 +48218,10 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.97014444134469</v>
+        <v>-4.09734589179938</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.394236463028214</v>
+        <v>2.343355882846339</v>
       </c>
       <c r="F2029" t="n">
         <v>0.7132533186198635</v>
@@ -48241,10 +48241,10 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.025099637787759</v>
+        <v>-4.152301088242449</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.373225562203697</v>
+        <v>2.322344982021821</v>
       </c>
       <c r="F2030" t="n">
         <v>0.7132533186198635</v>
@@ -48264,10 +48264,10 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.974061261781239</v>
+        <v>-4.101262712235929</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.39448381698606</v>
+        <v>2.343603236804185</v>
       </c>
       <c r="F2031" t="n">
         <v>0.7132533186198635</v>
@@ -48287,10 +48287,10 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.932921966914608</v>
+        <v>-4.060123417369298</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.429977633806859</v>
+        <v>2.379097053624982</v>
       </c>
       <c r="F2032" t="n">
         <v>0.7543926134864943</v>
@@ -48310,10 +48310,10 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.822315826835006</v>
+        <v>-3.949517277289696</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.290404085962634</v>
+        <v>2.239523505780758</v>
       </c>
       <c r="F2033" t="n">
         <v>0.8649987535660963</v>
@@ -48333,10 +48333,10 @@
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.952896561365849</v>
+        <v>-4.080098011820539</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.24167383622426</v>
+        <v>2.190793256042384</v>
       </c>
       <c r="F2034" t="n">
         <v>0.7344180190352538</v>
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.842510502870751</v>
+        <v>3.788377674709727</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.819820666901524</v>
+        <v>3.772397547303264</v>
       </c>
       <c r="D2035" t="n">
-        <v>-3.952896561365849</v>
+        <v>-4.080098011820539</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.24167383622426</v>
+        <v>2.190793256042384</v>
       </c>
       <c r="F2035" t="n">
         <v>0.7344180190352538</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.812884463887892</v>
+        <v>3.765461344289632</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-569.6%</t>
+          <t>-563.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-154.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-128.1%</t>
+          <t>-127.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.6%</t>
+          <t>-152.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.538080175137778</v>
+        <v>-3.514119241689489</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.357260226975495</v>
+        <v>1.36684460035481</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5607311223308068</v>
@@ -46999,10 +46999,10 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.49370704349921</v>
+        <v>-3.46974611005092</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.374872347066358</v>
+        <v>1.384456720445674</v>
       </c>
       <c r="F1976" t="n">
         <v>0.6051042539693754</v>
@@ -47022,10 +47022,10 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.370872822612042</v>
+        <v>-3.346911889163753</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.418399829559816</v>
+        <v>1.427984202939132</v>
       </c>
       <c r="F1977" t="n">
         <v>0.6051042539693754</v>
@@ -47045,10 +47045,10 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.323217092050987</v>
+        <v>-3.299256158602697</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.443843878812043</v>
+        <v>1.453428252191359</v>
       </c>
       <c r="F1978" t="n">
         <v>0.652759984530431</v>
@@ -47068,10 +47068,10 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.222698933552232</v>
+        <v>-3.198738000103942</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.488943515586269</v>
+        <v>1.498527888965585</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7532781430291856</v>
@@ -47091,10 +47091,10 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.283365523954621</v>
+        <v>-3.259404590506331</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.451431551901186</v>
+        <v>1.461015925280502</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6715798263106519</v>
@@ -47114,10 +47114,10 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.238527122346223</v>
+        <v>-3.214566188897933</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.473464615155174</v>
+        <v>1.48304898853449</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6761232592555214</v>
@@ -47137,10 +47137,10 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.258025578588231</v>
+        <v>-3.234064645139942</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.469826172289448</v>
+        <v>1.479410545668765</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6280386179756171</v>
@@ -47160,10 +47160,10 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.213822741502331</v>
+        <v>-3.189861808054041</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.493386909651646</v>
+        <v>1.502971283030962</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6722414550615176</v>
@@ -47183,10 +47183,10 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.250801769165774</v>
+        <v>-3.226840835717484</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.477005299055516</v>
+        <v>1.486589672434832</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7092153568528481</v>
@@ -47206,10 +47206,10 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.092510351626502</v>
+        <v>-3.068549418178212</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.591569631254265</v>
+        <v>1.601154004633581</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7092153568528481</v>
@@ -47229,10 +47229,10 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.884868347992026</v>
+        <v>-2.860907414543736</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.673067137302308</v>
+        <v>1.682651510681624</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9168573604873242</v>
@@ -47252,10 +47252,10 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.833836255269498</v>
+        <v>-2.809875321821208</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.688428202629589</v>
+        <v>1.698012576008906</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9678894532098522</v>
@@ -47275,10 +47275,10 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.768612074142292</v>
+        <v>-2.744651140694002</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.731705279173177</v>
+        <v>1.741289652552493</v>
       </c>
       <c r="F1988" t="n">
         <v>1.033113634337058</v>
@@ -47298,10 +47298,10 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.731185054071159</v>
+        <v>-2.707224120622869</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.74263705950091</v>
+        <v>1.752221432880226</v>
       </c>
       <c r="F1989" t="n">
         <v>1.038365172366239</v>
@@ -47321,10 +47321,10 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.751296710105867</v>
+        <v>-2.727335776657577</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.735849189418267</v>
+        <v>1.745433562797583</v>
       </c>
       <c r="F1990" t="n">
         <v>1.049392517363658</v>
@@ -47344,10 +47344,10 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.697551895678662</v>
+        <v>-2.673590962230372</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.91790488621036</v>
+        <v>1.927489259589676</v>
       </c>
       <c r="F1991" t="n">
         <v>1.059455826804121</v>
@@ -47367,10 +47367,10 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.62276963465365</v>
+        <v>-2.59880870120536</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.067930699838183</v>
+        <v>2.077515073217498</v>
       </c>
       <c r="F1992" t="n">
         <v>1.134238087829133</v>
@@ -47390,10 +47390,10 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.596685550389842</v>
+        <v>-2.572724616941552</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.070072309557564</v>
+        <v>2.07965668293688</v>
       </c>
       <c r="F1993" t="n">
         <v>1.134238087829133</v>
@@ -47413,10 +47413,10 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.518554369540895</v>
+        <v>-2.494593436092605</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.099517977480923</v>
+        <v>2.109102350860239</v>
       </c>
       <c r="F1994" t="n">
         <v>1.208414898712818</v>
@@ -47436,10 +47436,10 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.509661908147612</v>
+        <v>-2.485700974699322</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.120629367765027</v>
+        <v>2.130213741144343</v>
       </c>
       <c r="F1995" t="n">
         <v>1.208414898712818</v>
@@ -47459,10 +47459,10 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.67813802511749</v>
+        <v>-2.6541770916692</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.04509396838166</v>
+        <v>2.054678341760976</v>
       </c>
       <c r="F1996" t="n">
         <v>1.180467062996237</v>
@@ -47482,10 +47482,10 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.980338496255906</v>
+        <v>-1.956377562807616</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.305483477114155</v>
+        <v>2.315067850493471</v>
       </c>
       <c r="F1997" t="n">
         <v>1.110119003625826</v>
@@ -47505,10 +47505,10 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.957617392572754</v>
+        <v>-1.933656459124464</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.305235941084321</v>
+        <v>2.314820314463637</v>
       </c>
       <c r="F1998" t="n">
         <v>1.110119003625826</v>
@@ -47528,10 +47528,10 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.086819205866796</v>
+        <v>-2.062858272418506</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.412461341617873</v>
+        <v>2.422045714997189</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9809171903317842</v>
@@ -47551,10 +47551,10 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.241600212645052</v>
+        <v>-2.217639279196762</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.387626761400217</v>
+        <v>2.397211134779533</v>
       </c>
       <c r="F2000" t="n">
         <v>0.947549516277308</v>
@@ -47574,10 +47574,10 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.234545522429878</v>
+        <v>-2.210584588981588</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.387123993475832</v>
+        <v>2.396708366855148</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9546042064924818</v>
@@ -47597,10 +47597,10 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.20759429810339</v>
+        <v>-2.1836333646551</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.407910636851168</v>
+        <v>2.417495010230485</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9694845525202009</v>
@@ -47620,10 +47620,10 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.343547306159707</v>
+        <v>-2.319586372711417</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.537632565773602</v>
+        <v>2.547216939152918</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9694845525202009</v>
@@ -47643,10 +47643,10 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.365955423964579</v>
+        <v>-2.341994490516289</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.520786013554646</v>
+        <v>2.530370386933962</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9694845525202009</v>
@@ -47666,10 +47666,10 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.513961191443978</v>
+        <v>-2.490000257995688</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.463637706112523</v>
+        <v>2.47322207949184</v>
       </c>
       <c r="F2005" t="n">
         <v>0.8827575436566595</v>
@@ -47689,10 +47689,10 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.523402117332508</v>
+        <v>-2.499441183884218</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.516115053478959</v>
+        <v>2.525699426858275</v>
       </c>
       <c r="F2006" t="n">
         <v>1.005184661200051</v>
@@ -47712,10 +47712,10 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.575675724668149</v>
+        <v>-2.551714791219859</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.498096705090003</v>
+        <v>2.507681078469319</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9529110538644098</v>
@@ -47735,10 +47735,10 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.652005702269055</v>
+        <v>-2.628044768820765</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.465676526943416</v>
+        <v>2.475260900322732</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9529110538644098</v>
@@ -47758,10 +47758,10 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.763762654884356</v>
+        <v>-2.739801721436066</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.415793975500158</v>
+        <v>2.425378348879474</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8411541012491086</v>
@@ -47781,10 +47781,10 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.761921635826105</v>
+        <v>-2.737960702377815</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.41496439333361</v>
+        <v>2.424548766712927</v>
       </c>
       <c r="F2010" t="n">
         <v>0.842422327920577</v>
@@ -47804,10 +47804,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.894222927923658</v>
+        <v>-2.870261994475368</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.375117283360508</v>
+        <v>2.384701656739824</v>
       </c>
       <c r="F2011" t="n">
         <v>0.842422327920577</v>
@@ -47827,10 +47827,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.895784570738519</v>
+        <v>-2.871823637290229</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.374492626234564</v>
+        <v>2.38407699961388</v>
       </c>
       <c r="F2012" t="n">
         <v>0.842422327920577</v>
@@ -47850,10 +47850,10 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.923685357847992</v>
+        <v>-2.899724424399702</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.361856352517777</v>
+        <v>2.371440725897092</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8078254037776422</v>
@@ -47873,10 +47873,10 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.046211460550885</v>
+        <v>-3.022250527102595</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.309610355413818</v>
+        <v>2.319194728793134</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6852993010747483</v>
@@ -47896,10 +47896,10 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.066272781827392</v>
+        <v>-3.042311848379102</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.368291786493719</v>
+        <v>2.377876159873035</v>
       </c>
       <c r="F2015" t="n">
         <v>0.6652379797982413</v>
@@ -47919,10 +47919,10 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.322993599822216</v>
+        <v>-3.299032666373926</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.405915178297636</v>
+        <v>2.415499551676953</v>
       </c>
       <c r="F2016" t="n">
         <v>0.5568234056544265</v>
@@ -47942,10 +47942,10 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.476980017598357</v>
+        <v>-3.453019084150067</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.41330088033282</v>
+        <v>2.422885253712136</v>
       </c>
       <c r="F2017" t="n">
         <v>0.5568234056544265</v>
@@ -47965,10 +47965,10 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.426458113770691</v>
+        <v>-3.402497180322401</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.419560843984007</v>
+        <v>2.429145217363323</v>
       </c>
       <c r="F2018" t="n">
         <v>0.5568234056544265</v>
@@ -47988,10 +47988,10 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.678933267778415</v>
+        <v>-3.654972334330125</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.330441271436332</v>
+        <v>2.340025644815647</v>
       </c>
       <c r="F2019" t="n">
         <v>0.5568234056544265</v>
@@ -48011,10 +48011,10 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.948406069700123</v>
+        <v>-3.924445136251833</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.223862685186592</v>
+        <v>2.233447058565908</v>
       </c>
       <c r="F2020" t="n">
         <v>0.5568234056544265</v>
@@ -48034,10 +48034,10 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.105950141429565</v>
+        <v>-4.081989207981275</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.164966798722137</v>
+        <v>2.174551172101453</v>
       </c>
       <c r="F2021" t="n">
         <v>0.489921600514152</v>
@@ -48057,10 +48057,10 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.383914537012839</v>
+        <v>-4.359953603564549</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.048858893225017</v>
+        <v>2.058443266604333</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4003018662286678</v>
@@ -48080,10 +48080,10 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.500882229651729</v>
+        <v>-4.476921296203439</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.164275872868505</v>
+        <v>2.173860246247821</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4003018662286678</v>
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.623661831620744</v>
+        <v>-4.561639238424393</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.110010670044713</v>
+        <v>2.134819707323254</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3367851668275899</v>
+        <v>0.3151858373006214</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.161902927103312</v>
+        <v>4.148943329387131</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.705596649889627</v>
+        <v>-4.643574056693276</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.087466160305651</v>
+        <v>2.112275197584192</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3268504212405097</v>
+        <v>0.3052510917135412</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.166171497319556</v>
+        <v>4.153211899603374</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.651858476489365</v>
+        <v>-4.589835883293014</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.117887068121658</v>
+        <v>2.142696105400199</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3805885946407718</v>
+        <v>0.3589892651138033</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.207340039815614</v>
+        <v>4.194380442099433</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.541852193012144</v>
+        <v>-4.479829599815792</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.154042468756722</v>
+        <v>2.178851506035263</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.403793166558047</v>
+        <v>0.3821938370310785</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.213415670210155</v>
+        <v>4.200456072493974</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.398792617271218</v>
+        <v>-4.336770024074866</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.215516309775067</v>
+        <v>2.240325347053608</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4118065931480263</v>
+        <v>0.3902072636210578</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.222473736886117</v>
+        <v>4.209514139169936</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.09734589179938</v>
+        <v>-4.035323298603029</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.343355882846339</v>
+        <v>2.368164920124879</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7132533186198635</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.410602655051756</v>
+        <v>4.397643057335575</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.152301088242449</v>
+        <v>-4.090278495046098</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.322344982021821</v>
+        <v>2.347154019300361</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7132533186198635</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.411573832804466</v>
+        <v>4.398614235088285</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.101262712235929</v>
+        <v>-4.039240119039578</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.343603236804185</v>
+        <v>2.368412274082725</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7132533186198635</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.412416737184222</v>
+        <v>4.399457139468041</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.060123417369298</v>
+        <v>-3.998100824172947</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.379097053624982</v>
+        <v>2.403906090903523</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7543926134864943</v>
+        <v>0.7327932839595258</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.456138412978346</v>
+        <v>4.443178815262165</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.949517277289696</v>
+        <v>-3.887494684093345</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.239523505780758</v>
+        <v>2.264332543059298</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8649987535660963</v>
+        <v>0.8433994240391278</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.338686093150042</v>
+        <v>4.325726495433861</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462782</v>
+        <v>3.804703121462783</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.080098011820539</v>
+        <v>-4.018075418624187</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.190793256042384</v>
+        <v>2.215602293320925</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7344180190352538</v>
+        <v>0.7128186895082853</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.263839696505499</v>
+        <v>4.250880098789318</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.788377674709727</v>
+        <v>3.788377674709728</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.772397547303264</v>
+        <v>3.762623735542653</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.080098011820539</v>
+        <v>-4.018075418624187</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.190793256042384</v>
+        <v>2.215602293320925</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7344180190352538</v>
+        <v>0.7128186895082853</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.765461344289632</v>
+        <v>3.755687532529021</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.9%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-563.4%</t>
+          <t>-565.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.7%</t>
+          <t>-161.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.7%</t>
+          <t>-119.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-166.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-35.7%</t>
         </is>
       </c>
     </row>
@@ -47574,16 +47574,16 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.210584588981588</v>
+        <v>-2.352965516936675</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.396708366855148</v>
+        <v>2.339755995673113</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9546042064924818</v>
+        <v>0.8122232785373944</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.854061150657019</v>
+        <v>3.768632593883967</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.1836333646551</v>
+        <v>-2.326014292610187</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.417495010230485</v>
+        <v>2.360542639048449</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8271036245651135</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.872995511918393</v>
+        <v>3.78756695514534</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.319586372711417</v>
+        <v>-2.461967300666504</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.547216939152918</v>
+        <v>2.490264567970883</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8271036245651135</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.057098644063353</v>
+        <v>3.9716700872903</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.341994490516289</v>
+        <v>-2.484375418471376</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.530370386933962</v>
+        <v>2.473418015751927</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.8271036245651135</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.049215338966346</v>
+        <v>3.963786782193293</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.490000257995688</v>
+        <v>-2.632381185950775</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.47322207949184</v>
+        <v>2.416269708309805</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8827575436566595</v>
+        <v>0.7403766157015721</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999233133197858</v>
+        <v>3.913804576424806</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.499441183884218</v>
+        <v>-2.641822111839305</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.525699426858275</v>
+        <v>2.46874705567624</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.005184661200051</v>
+        <v>0.8628037332449635</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.12894312144574</v>
+        <v>4.043514564672687</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.551714791219859</v>
+        <v>-2.694095719174947</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.507681078469319</v>
+        <v>2.450728707287285</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8105301259093223</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100470051589657</v>
+        <v>4.015041494816604</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.628044768820765</v>
+        <v>-2.770425696775852</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.475260900322732</v>
+        <v>2.418308529140697</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8105301259093223</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098581864483432</v>
+        <v>4.013153307710379</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.739801721436066</v>
+        <v>-2.882182649391154</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.425378348879474</v>
+        <v>2.368425977697439</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8411541012491086</v>
+        <v>0.6987731732940212</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.026347922517113</v>
+        <v>3.940919365744061</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.737960702377815</v>
+        <v>-2.880341630332902</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.424548766712927</v>
+        <v>2.367596395530892</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7000413999654896</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.025542868730146</v>
+        <v>3.940114311957094</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.870261994475368</v>
+        <v>-3.012642922430456</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.384701656739824</v>
+        <v>2.327749285557789</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7000413999654896</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.038616275596065</v>
+        <v>3.953187718823012</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.871823637290229</v>
+        <v>-3.014204565245316</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.38407699961388</v>
+        <v>2.327124628431845</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7000413999654896</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.038616275596065</v>
+        <v>3.953187718823012</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.899724424399702</v>
+        <v>-3.042105352354789</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.371440725897092</v>
+        <v>2.314488354715058</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8078254037776422</v>
+        <v>0.6654444758225548</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.016382162237306</v>
+        <v>3.930953605464254</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.022250527102595</v>
+        <v>-3.164631455057683</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.319194728793134</v>
+        <v>2.262242357611099</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6852993010747483</v>
+        <v>0.542918373119661</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.939630944592769</v>
+        <v>3.854202387819716</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.042311848379102</v>
+        <v>-3.184692776334189</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.377876159873035</v>
+        <v>2.320923788691</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6652379797982413</v>
+        <v>0.5228570518431539</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.994300111417368</v>
+        <v>3.908871554644316</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.299032666373926</v>
+        <v>-3.441413594329013</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.415499551676953</v>
+        <v>2.358547180494917</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4144424776993391</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.069563085932926</v>
+        <v>3.984134529159874</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.453019084150067</v>
+        <v>-3.595400012105154</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.422885253712136</v>
+        <v>2.365932882530101</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4144424776993391</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.138543355078566</v>
+        <v>4.053114798305514</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.402497180322401</v>
+        <v>-3.544878108277488</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.429145217363323</v>
+        <v>2.372192846181288</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4144424776993391</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.124594557198687</v>
+        <v>4.039166000425634</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.654972334330125</v>
+        <v>-3.797353262285212</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.340025644815647</v>
+        <v>2.283073273633613</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4144424776993391</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.136465046254101</v>
+        <v>4.051036489481048</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.924445136251833</v>
+        <v>-4.06682606420692</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.233447058565908</v>
+        <v>2.176494687383873</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4144424776993391</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.137675580773045</v>
+        <v>4.052247023999993</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.081989207981275</v>
+        <v>-4.224370135936362</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.174551172101453</v>
+        <v>2.117598800919418</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.489921600514152</v>
+        <v>0.3475406725590646</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.101656239916202</v>
+        <v>4.016227683143149</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.359953603564549</v>
+        <v>-4.502334531519636</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.058443266604333</v>
+        <v>2.001490895422298</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2579209382735803</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.0429622520811</v>
+        <v>3.957533695308048</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.476921296203439</v>
+        <v>-4.619302224158527</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.173860246247821</v>
+        <v>2.116907875065785</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2579209382735803</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.205166308780145</v>
+        <v>4.119737752007092</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.561639238424393</v>
+        <v>-4.70402016637948</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.134819707323254</v>
+        <v>2.077867336141218</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3151858373006214</v>
+        <v>0.1728049093455339</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.148943329387131</v>
+        <v>4.063514772614078</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.643574056693276</v>
+        <v>-4.785954984648363</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.112275197584192</v>
+        <v>2.055322826402157</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3052510917135412</v>
+        <v>0.1628701637584538</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.153211899603374</v>
+        <v>4.067783342830322</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.589835883293014</v>
+        <v>-4.732216811248101</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.142696105400199</v>
+        <v>2.085743734218164</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3589892651138033</v>
+        <v>0.2166083371587159</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.194380442099433</v>
+        <v>4.108951885326381</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.479829599815792</v>
+        <v>-4.622210527770879</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.178851506035263</v>
+        <v>2.121899134853228</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3821938370310785</v>
+        <v>0.2398129090759911</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.200456072493974</v>
+        <v>4.115027515720922</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.336770024074866</v>
+        <v>-4.479150952029954</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.240325347053608</v>
+        <v>2.183372975871572</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3902072636210578</v>
+        <v>0.2478263356659703</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.209514139169936</v>
+        <v>4.124085582396884</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.035323298603029</v>
+        <v>-4.177704226558117</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.368164920124879</v>
+        <v>2.311212548942844</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5492730611378076</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.397643057335575</v>
+        <v>4.312214500562523</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.090278495046098</v>
+        <v>-4.232659423001186</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.347154019300361</v>
+        <v>2.290201648118326</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5492730611378076</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.398614235088285</v>
+        <v>4.313185678315233</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.039240119039578</v>
+        <v>-4.181621046994666</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.368412274082725</v>
+        <v>2.31145990290069</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5492730611378076</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.399457139468041</v>
+        <v>4.314028582694989</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.998100824172947</v>
+        <v>-4.140481752128035</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.403906090903523</v>
+        <v>2.346953719721488</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7327932839595258</v>
+        <v>0.5904123560044384</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.443178815262165</v>
+        <v>4.357750258489112</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.887494684093345</v>
+        <v>-4.029875612048433</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.264332543059298</v>
+        <v>2.207380171877263</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8433994240391278</v>
+        <v>0.7010184960840404</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.325726495433861</v>
+        <v>4.240297938660808</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.018075418624187</v>
+        <v>-4.160456346579275</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.215602293320925</v>
+        <v>2.15864992213889</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.5704377615531979</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.250880098789318</v>
+        <v>4.165451542016267</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.788377674709728</v>
+        <v>3.701017746555379</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.762623735542653</v>
+        <v>3.760614934589414</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.018075418624187</v>
+        <v>-4.040130429722961</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.215602293320925</v>
+        <v>2.144206338386483</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.5704377615531979</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.755687532529021</v>
+        <v>4.102877591521334</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240724.xlsx
+++ b/tame_output/ON/bt/strategyON_20240724.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>455.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.6%</t>
+          <t>-568.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.8%</t>
+          <t>-168.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-119.7%</t>
+          <t>-103.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-174.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-46.2%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.514119241689489</v>
+        <v>-3.410878724683089</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.36684460035481</v>
+        <v>1.40814080715737</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5607311223308068</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.46974611005092</v>
+        <v>-3.366505593044521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.384456720445674</v>
+        <v>1.425752927248234</v>
       </c>
       <c r="F1976" t="n">
         <v>0.6051042539693754</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.346911889163753</v>
+        <v>-3.243671372157353</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.427984202939132</v>
+        <v>1.469280409741691</v>
       </c>
       <c r="F1977" t="n">
         <v>0.6051042539693754</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.299256158602697</v>
+        <v>-3.196015641596298</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.453428252191359</v>
+        <v>1.494724458993918</v>
       </c>
       <c r="F1978" t="n">
         <v>0.652759984530431</v>
@@ -47068,10 +47068,10 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.198738000103942</v>
+        <v>-3.095497483097543</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.498527888965585</v>
+        <v>1.539824095768145</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7532781430291856</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.259404590506331</v>
+        <v>-3.156164073499932</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.461015925280502</v>
+        <v>1.502312132083061</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6715798263106519</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.214566188897933</v>
+        <v>-3.111325671891534</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.48304898853449</v>
+        <v>1.524345195337049</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6761232592555214</v>
@@ -47137,10 +47137,10 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.234064645139942</v>
+        <v>-3.130824128133542</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.479410545668765</v>
+        <v>1.520706752471324</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6280386179756171</v>
@@ -47160,10 +47160,10 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.189861808054041</v>
+        <v>-3.086621291047642</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.502971283030962</v>
+        <v>1.544267489833521</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6722414550615176</v>
@@ -47183,10 +47183,10 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.226840835717484</v>
+        <v>-3.123600318711085</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.486589672434832</v>
+        <v>1.527885879237392</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7092153568528481</v>
@@ -47206,10 +47206,10 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.068549418178212</v>
+        <v>-2.965308901171813</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.601154004633581</v>
+        <v>1.64245021143614</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7092153568528481</v>
@@ -47229,10 +47229,10 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.860907414543736</v>
+        <v>-2.757666897537337</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.682651510681624</v>
+        <v>1.723947717484184</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9168573604873242</v>
@@ -47252,10 +47252,10 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.809875321821208</v>
+        <v>-2.706634804814809</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.698012576008906</v>
+        <v>1.739308782811465</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9678894532098522</v>
@@ -47275,10 +47275,10 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.744651140694002</v>
+        <v>-2.641410623687603</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.741289652552493</v>
+        <v>1.782585859355052</v>
       </c>
       <c r="F1988" t="n">
         <v>1.033113634337058</v>
@@ -47298,10 +47298,10 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.707224120622869</v>
+        <v>-2.60398360361647</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.752221432880226</v>
+        <v>1.793517639682786</v>
       </c>
       <c r="F1989" t="n">
         <v>1.038365172366239</v>
@@ -47321,10 +47321,10 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.727335776657577</v>
+        <v>-2.624095259651178</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.745433562797583</v>
+        <v>1.786729769600143</v>
       </c>
       <c r="F1990" t="n">
         <v>1.049392517363658</v>
@@ -47344,10 +47344,10 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.673590962230372</v>
+        <v>-2.570350445223973</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.927489259589676</v>
+        <v>1.968785466392236</v>
       </c>
       <c r="F1991" t="n">
         <v>1.059455826804121</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.59880870120536</v>
+        <v>-2.495568184198961</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.077515073217498</v>
+        <v>2.118811280020058</v>
       </c>
       <c r="F1992" t="n">
         <v>1.134238087829133</v>
@@ -47390,10 +47390,10 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.572724616941552</v>
+        <v>-2.469484099935153</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.07965668293688</v>
+        <v>2.12095288973944</v>
       </c>
       <c r="F1993" t="n">
         <v>1.134238087829133</v>
@@ -47413,10 +47413,10 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.494593436092605</v>
+        <v>-2.391352919086206</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.109102350860239</v>
+        <v>2.150398557662798</v>
       </c>
       <c r="F1994" t="n">
         <v>1.208414898712818</v>
@@ -47436,10 +47436,10 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.485700974699322</v>
+        <v>-2.382460457692923</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.130213741144343</v>
+        <v>2.171509947946903</v>
       </c>
       <c r="F1995" t="n">
         <v>1.208414898712818</v>
@@ -47459,10 +47459,10 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.6541770916692</v>
+        <v>-2.550936574662801</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.054678341760976</v>
+        <v>2.095974548563536</v>
       </c>
       <c r="F1996" t="n">
         <v>1.180467062996237</v>
@@ -47482,10 +47482,10 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.956377562807616</v>
+        <v>-1.853137045801217</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.315067850493471</v>
+        <v>2.356364057296031</v>
       </c>
       <c r="F1997" t="n">
         <v>1.110119003625826</v>
@@ -47505,10 +47505,10 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.933656459124464</v>
+        <v>-1.830415942118065</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.314820314463637</v>
+        <v>2.356116521266197</v>
       </c>
       <c r="F1998" t="n">
         <v>1.110119003625826</v>
@@ -47528,10 +47528,10 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.062858272418506</v>
+        <v>-1.959617755412107</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.422045714997189</v>
+        <v>2.463341921799748</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9809171903317842</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.217639279196762</v>
+        <v>-2.114398762190362</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.397211134779533</v>
+        <v>2.438507341582093</v>
       </c>
       <c r="F2000" t="n">
         <v>0.947549516277308</v>
@@ -47574,16 +47574,16 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.352965516936675</v>
+        <v>-2.232724091734897</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.339755995673113</v>
+        <v>2.387852565753824</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8122232785373944</v>
+        <v>0.8292241867327735</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.768632593883967</v>
+        <v>3.778833138801195</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.326014292610187</v>
+        <v>-2.205772867408409</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.360542639048449</v>
+        <v>2.408639209129161</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8271036245651135</v>
+        <v>0.8441045327604927</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.78756695514534</v>
+        <v>3.797767500062568</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.461967300666504</v>
+        <v>-2.341725875464725</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.490264567970883</v>
+        <v>2.538361138051594</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8271036245651135</v>
+        <v>0.8441045327604927</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.9716700872903</v>
+        <v>3.981870632207528</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.484375418471376</v>
+        <v>-2.364133993269597</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.473418015751927</v>
+        <v>2.521514585832639</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8271036245651135</v>
+        <v>0.8441045327604927</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.963786782193293</v>
+        <v>3.973987327110521</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.632381185950775</v>
+        <v>-2.512139760748997</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.416269708309805</v>
+        <v>2.464366278390516</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7403766157015721</v>
+        <v>0.7573775238969512</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.913804576424806</v>
+        <v>3.924005121342033</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.641822111839305</v>
+        <v>-2.521580686637527</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.46874705567624</v>
+        <v>2.516843625756952</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8628037332449635</v>
+        <v>0.8798046414403426</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.043514564672687</v>
+        <v>4.053715109589915</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.694095719174947</v>
+        <v>-2.573854293973168</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.450728707287285</v>
+        <v>2.498825277367996</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8105301259093223</v>
+        <v>0.8275310341047014</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.015041494816604</v>
+        <v>4.025242039733831</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.770425696775852</v>
+        <v>-2.650184271574074</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.418308529140697</v>
+        <v>2.466405099221409</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8105301259093223</v>
+        <v>0.8275310341047014</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.013153307710379</v>
+        <v>4.023353852627606</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.882182649391154</v>
+        <v>-2.761941224189375</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.368425977697439</v>
+        <v>2.41652254777815</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6987731732940212</v>
+        <v>0.7157740814894002</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.940919365744061</v>
+        <v>3.951119910661288</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.880341630332902</v>
+        <v>-2.760100205131124</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.367596395530892</v>
+        <v>2.415692965611603</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7000413999654896</v>
+        <v>0.7170423081608687</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.940114311957094</v>
+        <v>3.950314856874321</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.012642922430456</v>
+        <v>-2.892401497228677</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.327749285557789</v>
+        <v>2.3758458556385</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7000413999654896</v>
+        <v>0.7170423081608687</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.953187718823012</v>
+        <v>3.96338826374024</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.014204565245316</v>
+        <v>-2.893963140043537</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.327124628431845</v>
+        <v>2.375221198512556</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7000413999654896</v>
+        <v>0.7170423081608687</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.953187718823012</v>
+        <v>3.96338826374024</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.042105352354789</v>
+        <v>-2.92186392715301</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.314488354715058</v>
+        <v>2.362584924795769</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6654444758225548</v>
+        <v>0.6824453840179339</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.930953605464254</v>
+        <v>3.941154150381482</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.164631455057683</v>
+        <v>-3.044390029855904</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.262242357611099</v>
+        <v>2.31033892769181</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.542918373119661</v>
+        <v>0.55991928131504</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.854202387819716</v>
+        <v>3.864402932736944</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.184692776334189</v>
+        <v>-3.064451351132411</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.320923788691</v>
+        <v>2.369020358771712</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5228570518431539</v>
+        <v>0.5398579600385329</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.908871554644316</v>
+        <v>3.919072099561543</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.441413594329013</v>
+        <v>-3.321172169127235</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.358547180494917</v>
+        <v>2.406643750575629</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4144424776993391</v>
+        <v>0.4314433858947181</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.984134529159874</v>
+        <v>3.994335074077101</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.595400012105154</v>
+        <v>-3.475158586903375</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.365932882530101</v>
+        <v>2.414029452610813</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4144424776993391</v>
+        <v>0.4314433858947181</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.053114798305514</v>
+        <v>4.063315343222741</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.544878108277488</v>
+        <v>-3.424636683075709</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.372192846181288</v>
+        <v>2.420289416262</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4144424776993391</v>
+        <v>0.4314433858947181</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.039166000425634</v>
+        <v>4.049366545342862</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.797353262285212</v>
+        <v>-3.677111837083434</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.283073273633613</v>
+        <v>2.331169843714324</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4144424776993391</v>
+        <v>0.4314433858947181</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.051036489481048</v>
+        <v>4.061237034398276</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.06682606420692</v>
+        <v>-3.946584639005142</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.176494687383873</v>
+        <v>2.224591257464585</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4144424776993391</v>
+        <v>0.4314433858947181</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.052247023999993</v>
+        <v>4.06244756891722</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.224370135936362</v>
+        <v>-4.104128710734583</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.117598800919418</v>
+        <v>2.165695371000129</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3475406725590646</v>
+        <v>0.3645415807544436</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.016227683143149</v>
+        <v>4.026428228060376</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.502334531519636</v>
+        <v>-4.382093106317857</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.001490895422298</v>
+        <v>2.049587465503009</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2579209382735803</v>
+        <v>0.2749218464689593</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.957533695308048</v>
+        <v>3.967734240225275</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.619302224158527</v>
+        <v>-4.499060798956748</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.116907875065785</v>
+        <v>2.165004445146497</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2579209382735803</v>
+        <v>0.2749218464689593</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.119737752007092</v>
+        <v>4.129938296924319</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.70402016637948</v>
+        <v>-4.583778741177701</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.077867336141218</v>
+        <v>2.12596390622193</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1728049093455339</v>
+        <v>0.189805817540913</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.063514772614078</v>
+        <v>4.073715317531306</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.785954984648363</v>
+        <v>-4.738856694231012</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.055322826402157</v>
+        <v>2.074162142569097</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1628701637584538</v>
+        <v>0.0870921863102071</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.067783342830322</v>
+        <v>4.022316556361374</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.732216811248101</v>
+        <v>-4.685118520830749</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.085743734218164</v>
+        <v>2.104583050385104</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2166083371587159</v>
+        <v>0.1408303597104692</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.108951885326381</v>
+        <v>4.063485098857433</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.622210527770879</v>
+        <v>-4.575112237353528</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.121899134853228</v>
+        <v>2.140738451020169</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2398129090759911</v>
+        <v>0.1640349316277444</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.115027515720922</v>
+        <v>4.069560729251974</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.479150952029954</v>
+        <v>-4.432052661612602</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.183372975871572</v>
+        <v>2.202212292038514</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2478263356659703</v>
+        <v>0.1720483582177237</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.124085582396884</v>
+        <v>4.078618795927936</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.177704226558117</v>
+        <v>-4.130605936140764</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.311212548942844</v>
+        <v>2.330051865109785</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5492730611378076</v>
+        <v>0.4734950836895609</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.312214500562523</v>
+        <v>4.266747714093575</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.232659423001186</v>
+        <v>-4.185561132583834</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.290201648118326</v>
+        <v>2.309040964285267</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5492730611378076</v>
+        <v>0.4734950836895609</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.313185678315233</v>
+        <v>4.267718891846285</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.181621046994666</v>
+        <v>-4.134522756577313</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.31145990290069</v>
+        <v>2.330299219067631</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5492730611378076</v>
+        <v>0.4734950836895609</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.314028582694989</v>
+        <v>4.268561796226041</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.140481752128035</v>
+        <v>-4.093383461710682</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.346953719721488</v>
+        <v>2.365793035888429</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5904123560044384</v>
+        <v>0.5146343785561918</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.357750258489112</v>
+        <v>4.312283472020164</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.029875612048433</v>
+        <v>-3.98277732163108</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.207380171877263</v>
+        <v>2.226219488044204</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7010184960840404</v>
+        <v>0.6252405186357938</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.240297938660808</v>
+        <v>4.19483115219186</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462783</v>
+        <v>3.804703121462782</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.160456346579275</v>
+        <v>-4.113358056161923</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.15864992213889</v>
+        <v>2.177489238305831</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5704377615531979</v>
+        <v>0.4946597841049513</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.165451542016267</v>
+        <v>4.119984755547319</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.701017746555379</v>
+        <v>3.841869802436204</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.760614934589414</v>
+        <v>3.701322102444774</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.040130429722961</v>
+        <v>-4.066121624061442</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.144206338386483</v>
+        <v>2.07451702850645</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5704377615531979</v>
+        <v>0.4946597841049513</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.102877591521334</v>
+        <v>3.998117972907745</v>
       </c>
     </row>
   </sheetData>
